--- a/research/traditional_assets/database/data/tunisia/tunisia_computer_services.xlsx
+++ b/research/traditional_assets/database/data/tunisia/tunisia_computer_services.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="earnings_debt" sheetId="1" r:id="rId1"/>
+    <sheet name="cost_capital" sheetId="2" r:id="rId2"/>
+    <sheet name="bvmt_tlnet" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -351,7 +353,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ3"/>
+  <dimension ref="A1:AQ4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +581,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,106 +590,115 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.11</v>
+        <v>-0.14445</v>
+      </c>
+      <c r="E2">
+        <v>-0.135</v>
       </c>
       <c r="G2">
-        <v>0.03233082706766917</v>
+        <v>0.1690357674347001</v>
       </c>
       <c r="H2">
-        <v>0.03233082706766917</v>
+        <v>0.1689844511725766</v>
       </c>
       <c r="I2">
-        <v>-0.004887218045112781</v>
+        <v>0.1413249858880279</v>
       </c>
       <c r="J2">
-        <v>-0.004887218045112781</v>
+        <v>0.1318125219979772</v>
       </c>
       <c r="K2">
-        <v>-0.18</v>
+        <v>3.497</v>
       </c>
       <c r="L2">
-        <v>-0.06766917293233082</v>
+        <v>0.1794529686457638</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>0.06994371970460977</v>
       </c>
       <c r="O2">
-        <v>-0</v>
+        <v>0.6148126965970833</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q2">
-        <v>0</v>
+        <v>0.06994371970460977</v>
       </c>
       <c r="R2">
-        <v>-0</v>
+        <v>0.6148126965970833</v>
       </c>
       <c r="S2">
         <v>0</v>
       </c>
+      <c r="T2">
+        <v>0</v>
+      </c>
       <c r="U2">
-        <v>0.003</v>
+        <v>4.601</v>
       </c>
       <c r="V2">
-        <v>0.005102040816326531</v>
+        <v>0.1496795601678649</v>
       </c>
       <c r="W2">
-        <v>0.1040462427745665</v>
+        <v>-0.1151272577996716</v>
       </c>
       <c r="X2">
-        <v>0.7108816574032684</v>
+        <v>0.5889833806184838</v>
       </c>
       <c r="Y2">
-        <v>-0.6068354146287018</v>
+        <v>-0.7041106384181554</v>
+      </c>
+      <c r="Z2">
+        <v>2.879710359095611</v>
       </c>
       <c r="AB2">
-        <v>0.2790928150182445</v>
+        <v>0.2389301883745155</v>
       </c>
       <c r="AD2">
-        <v>1.68</v>
+        <v>1.522</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>1.68</v>
+        <v>1.522</v>
       </c>
       <c r="AG2">
-        <v>1.677</v>
+        <v>-3.079</v>
       </c>
       <c r="AH2">
-        <v>0.7407407407407408</v>
+        <v>0.04717770682867858</v>
       </c>
       <c r="AI2">
-        <v>-27.99999999999998</v>
+        <v>0.1279852001345442</v>
       </c>
       <c r="AJ2">
-        <v>0.7403973509933774</v>
+        <v>-0.1113159797541576</v>
       </c>
       <c r="AK2">
-        <v>-26.61904761904764</v>
+        <v>-0.4223014675627485</v>
       </c>
       <c r="AL2">
-        <v>0.156</v>
+        <v>0.122</v>
       </c>
       <c r="AM2">
-        <v>0.156</v>
+        <v>0.104</v>
       </c>
       <c r="AN2">
-        <v>73.04347826086956</v>
+        <v>0.497548218372017</v>
       </c>
       <c r="AO2">
-        <v>-0.08333333333333333</v>
+        <v>22.57377049180328</v>
       </c>
       <c r="AP2">
-        <v>72.91304347826087</v>
+        <v>-1.006538084341288</v>
       </c>
       <c r="AQ2">
-        <v>-0.08333333333333333</v>
+        <v>26.48076923076923</v>
       </c>
     </row>
     <row r="3">
@@ -698,115 +709,9021 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>Telnet Holding SA (BVMT:TLNET)</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Computer Services</t>
+        </is>
+      </c>
+      <c r="D3">
+        <v>0.0851</v>
+      </c>
+      <c r="E3">
+        <v>-0.135</v>
+      </c>
+      <c r="G3">
+        <v>0.1752631578947368</v>
+      </c>
+      <c r="H3">
+        <v>0.1752631578947368</v>
+      </c>
+      <c r="I3">
+        <v>0.1557894736842105</v>
+      </c>
+      <c r="J3">
+        <v>0.1353873227961545</v>
+      </c>
+      <c r="K3">
+        <v>2.68</v>
+      </c>
+      <c r="L3">
+        <v>0.1410526315789474</v>
+      </c>
+      <c r="M3">
+        <v>2.15</v>
+      </c>
+      <c r="N3">
+        <v>0.07049180327868852</v>
+      </c>
+      <c r="O3">
+        <v>0.8022388059701492</v>
+      </c>
+      <c r="P3">
+        <v>2.15</v>
+      </c>
+      <c r="Q3">
+        <v>0.07049180327868852</v>
+      </c>
+      <c r="R3">
+        <v>0.8022388059701492</v>
+      </c>
+      <c r="S3">
+        <v>0</v>
+      </c>
+      <c r="T3">
+        <v>0</v>
+      </c>
+      <c r="U3">
+        <v>4.6</v>
+      </c>
+      <c r="V3">
+        <v>0.1508196721311475</v>
+      </c>
+      <c r="W3">
+        <v>0.2392857142857143</v>
+      </c>
+      <c r="X3">
+        <v>0.2167304961591042</v>
+      </c>
+      <c r="Y3">
+        <v>0.02255521812661013</v>
+      </c>
+      <c r="Z3">
+        <v>2.807743460913256</v>
+      </c>
+      <c r="AA3">
+        <v>0.3801328702714549</v>
+      </c>
+      <c r="AB3">
+        <v>0.2157843606650619</v>
+      </c>
+      <c r="AC3">
+        <v>0.1643485096063931</v>
+      </c>
+      <c r="AD3">
+        <v>0.332</v>
+      </c>
+      <c r="AE3">
+        <v>0</v>
+      </c>
+      <c r="AF3">
+        <v>0.332</v>
+      </c>
+      <c r="AG3">
+        <v>-4.268</v>
+      </c>
+      <c r="AH3">
+        <v>0.01076803321224702</v>
+      </c>
+      <c r="AI3">
+        <v>0.02829867030344357</v>
+      </c>
+      <c r="AJ3">
+        <v>-0.1627020433058859</v>
+      </c>
+      <c r="AK3">
+        <v>-0.5984296130117778</v>
+      </c>
+      <c r="AL3">
+        <v>0.002</v>
+      </c>
+      <c r="AM3">
+        <v>-0.016</v>
+      </c>
+      <c r="AN3">
+        <v>0.1021538461538462</v>
+      </c>
+      <c r="AO3">
+        <v>1480</v>
+      </c>
+      <c r="AP3">
+        <v>-1.313230769230769</v>
+      </c>
+      <c r="AQ3">
+        <v>-185</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Tunisia</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
           <t>Advanced e-Technologies S.A (BVMT:AETEC)</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>Computer Services</t>
         </is>
       </c>
+      <c r="D4">
+        <v>-0.374</v>
+      </c>
+      <c r="G4">
+        <v>-0.07392197125256673</v>
+      </c>
+      <c r="H4">
+        <v>-0.07597535934291581</v>
+      </c>
+      <c r="I4">
+        <v>-0.4229979466119096</v>
+      </c>
+      <c r="J4">
+        <v>-0.4214503931486954</v>
+      </c>
+      <c r="K4">
+        <v>0.8169999999999999</v>
+      </c>
+      <c r="L4">
+        <v>1.677618069815195</v>
+      </c>
+      <c r="M4">
+        <v>-0</v>
+      </c>
+      <c r="N4">
+        <v>-0</v>
+      </c>
+      <c r="O4">
+        <v>-0</v>
+      </c>
+      <c r="P4">
+        <v>-0</v>
+      </c>
+      <c r="Q4">
+        <v>-0</v>
+      </c>
+      <c r="R4">
+        <v>-0</v>
+      </c>
+      <c r="S4">
+        <v>0</v>
+      </c>
+      <c r="U4">
+        <v>0.001</v>
+      </c>
+      <c r="V4">
+        <v>0.004184100418410042</v>
+      </c>
+      <c r="W4">
+        <v>-0.4695402298850574</v>
+      </c>
+      <c r="X4">
+        <v>0.9612362650778634</v>
+      </c>
+      <c r="Y4">
+        <v>-1.430776494962921</v>
+      </c>
+      <c r="AB4">
+        <v>0.2620760160839692</v>
+      </c>
+      <c r="AD4">
+        <v>1.19</v>
+      </c>
+      <c r="AE4">
+        <v>0</v>
+      </c>
+      <c r="AF4">
+        <v>1.19</v>
+      </c>
+      <c r="AG4">
+        <v>1.189</v>
+      </c>
+      <c r="AH4">
+        <v>0.8327501749475158</v>
+      </c>
+      <c r="AI4">
+        <v>7.437500000000004</v>
+      </c>
+      <c r="AJ4">
+        <v>0.8326330532212886</v>
+      </c>
+      <c r="AK4">
+        <v>7.477987421383647</v>
+      </c>
+      <c r="AL4">
+        <v>0.12</v>
+      </c>
+      <c r="AM4">
+        <v>0.12</v>
+      </c>
+      <c r="AN4">
+        <v>-6.230366492146596</v>
+      </c>
+      <c r="AO4">
+        <v>-1.716666666666667</v>
+      </c>
+      <c r="AP4">
+        <v>-6.225130890052356</v>
+      </c>
+      <c r="AQ4">
+        <v>-1.716666666666667</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AY2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>company_name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>exchange_ticker</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>industry_group</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>current_interest_coverage</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_interest_coverage</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_ebitda</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_ebitda</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_capital</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_capital</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>current_equity_value</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_equity_value</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>current_enterprise_value</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_enterprise_value</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_capital</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_capital</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_rating</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_rating</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_equity</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_equity</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>current_beta</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_beta</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_mv_debt</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_coverage_ratio</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_debt</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_interest_expense</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_depreciation</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_ebitda</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>country_default_spread</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>risk_free</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>market_capitalization</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_risk_premium</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>reported_debt_rating</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>marginal_tax_rate</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_max_percentage</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_method</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_drop_ebitda</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>reported_capital_spending</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>reported_interest_expense</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>reported_bv_debt</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>reported_cash</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_ev_implied_growth</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>flag_bankruptcy</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>flag_refinanced</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>rating_firm_type</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio_limit</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Telnet Holding SA (BVMT:TLNET)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>BVMT:TLNET</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Computer Services</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Tunisia</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>1394.5</v>
+      </c>
+      <c r="F2">
+        <v>4.55684679612464</v>
+      </c>
+      <c r="G2">
+        <v>0.102153846153846</v>
+      </c>
+      <c r="H2">
+        <v>3.69984</v>
+      </c>
+      <c r="I2">
+        <v>0.010768033212247</v>
+      </c>
+      <c r="J2">
+        <v>0.39</v>
+      </c>
+      <c r="K2">
+        <v>30.5</v>
+      </c>
+      <c r="L2">
+        <v>20.2553211027168</v>
+      </c>
+      <c r="M2">
+        <v>26.232</v>
+      </c>
+      <c r="N2">
+        <v>27.6798011027168</v>
+      </c>
+      <c r="O2">
+        <v>0.332</v>
+      </c>
+      <c r="P2">
+        <v>12.02448</v>
+      </c>
+      <c r="Q2">
+        <v>0.215784360665062</v>
+      </c>
+      <c r="R2">
+        <v>0.206527135456556</v>
+      </c>
+      <c r="S2">
+        <v>0.128865286664187</v>
+      </c>
+      <c r="T2">
+        <v>0.043265</v>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="W2">
+        <v>0.216730496159104</v>
+      </c>
+      <c r="X2">
+        <v>0.310907845010747</v>
+      </c>
+      <c r="Y2">
+        <v>1.00146925531558</v>
+      </c>
+      <c r="Z2">
+        <v>1.53153982476824</v>
+      </c>
+      <c r="AA2">
+        <v>0.332</v>
+      </c>
+      <c r="AB2">
+        <v>0.151606219604926</v>
+      </c>
+      <c r="AC2">
+        <v>1394.5</v>
+      </c>
+      <c r="AD2">
+        <v>0.332</v>
+      </c>
+      <c r="AE2">
+        <v>0.002</v>
+      </c>
+      <c r="AF2">
+        <v>0.461</v>
+      </c>
+      <c r="AG2">
+        <v>3.25</v>
+      </c>
+      <c r="AH2">
+        <v>0</v>
+      </c>
+      <c r="AI2">
+        <v>0.0388</v>
+      </c>
+      <c r="AJ2">
+        <v>30.5</v>
+      </c>
+      <c r="AK2">
+        <v>0.1776694543688566</v>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="AM2">
+        <v>0.15</v>
+      </c>
+      <c r="AN2">
+        <v>0</v>
+      </c>
+      <c r="AO2">
+        <v>2</v>
+      </c>
+      <c r="AQ2">
+        <v>0.8179999999999998</v>
+      </c>
+      <c r="AR2">
+        <v>0.002</v>
+      </c>
+      <c r="AS2">
+        <v>0.332</v>
+      </c>
+      <c r="AT2">
+        <v>4.6</v>
+      </c>
+      <c r="AV2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AW2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AX2">
+        <v>1</v>
+      </c>
+      <c r="AY2">
+        <v>10000000</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Z101"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>debt_capital</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>cost_capital</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>equity_value</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>enterprise_value</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>debt_issued</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>debt</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>marketcap</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>drop_ebitda</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ebitda</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>depreciation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ebit</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>interest_expense</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>taxable_income</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>taxes</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>net_income</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>operating_cash_flow</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>debt_equity</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>beta</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>tax_rate</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>debt_rating</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>0.2150992941652214</v>
+      </c>
+      <c r="C2">
+        <v>30.93393270772243</v>
+      </c>
+      <c r="D2">
+        <v>26.33393270772243</v>
+      </c>
+      <c r="E2">
+        <v>-0.332</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>4.6</v>
+      </c>
+      <c r="H2">
+        <v>30.5</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>3.25</v>
+      </c>
+      <c r="K2">
+        <v>0.461</v>
+      </c>
+      <c r="L2">
+        <v>2.789</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>2.789</v>
+      </c>
+      <c r="O2">
+        <v>0.41835</v>
+      </c>
+      <c r="P2">
+        <v>2.37065</v>
+      </c>
+      <c r="Q2">
+        <v>2.83165</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0.2150992941652214</v>
+      </c>
+      <c r="T2">
+        <v>0.9922881498763958</v>
+      </c>
+      <c r="U2">
+        <v>0.0447</v>
+      </c>
+      <c r="V2">
+        <v>0.15</v>
+      </c>
+      <c r="W2">
+        <v>0.037995</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y2">
+        <v>10000000</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>0.01</v>
+      </c>
+      <c r="B3">
+        <v>0.2148267952239735</v>
+      </c>
+      <c r="C3">
+        <v>30.66637905112269</v>
+      </c>
       <c r="D3">
-        <v>-0.11</v>
+        <v>26.37469905112269</v>
+      </c>
+      <c r="E3">
+        <v>-0.02367999999999998</v>
+      </c>
+      <c r="F3">
+        <v>0.30832</v>
       </c>
       <c r="G3">
-        <v>0.03233082706766917</v>
+        <v>4.6</v>
       </c>
       <c r="H3">
-        <v>0.03233082706766917</v>
+        <v>30.5</v>
       </c>
       <c r="I3">
-        <v>-0.004887218045112781</v>
+        <v>0</v>
       </c>
       <c r="J3">
-        <v>-0.004887218045112781</v>
+        <v>3.25</v>
       </c>
       <c r="K3">
-        <v>-0.18</v>
+        <v>0.461</v>
       </c>
       <c r="L3">
-        <v>-0.06766917293233082</v>
+        <v>2.789</v>
       </c>
       <c r="M3">
-        <v>-0</v>
+        <v>0.013781904</v>
       </c>
       <c r="N3">
-        <v>-0</v>
+        <v>2.775218096</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>0.4162827144</v>
       </c>
       <c r="P3">
-        <v>-0</v>
+        <v>2.3589353816</v>
       </c>
       <c r="Q3">
-        <v>-0</v>
+        <v>2.8199353816</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>0.2166129749737107</v>
+      </c>
+      <c r="T3">
+        <v>1.000807795607658</v>
       </c>
       <c r="U3">
-        <v>0.003</v>
+        <v>0.0447</v>
       </c>
       <c r="V3">
-        <v>0.005102040816326531</v>
+        <v>0.15</v>
       </c>
       <c r="W3">
-        <v>0.1040462427745665</v>
-      </c>
-      <c r="X3">
-        <v>0.7108816574032684</v>
+        <v>0.037995</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
       </c>
       <c r="Y3">
-        <v>-0.6068354146287018</v>
-      </c>
-      <c r="AB3">
-        <v>0.2790928150182445</v>
-      </c>
-      <c r="AD3">
-        <v>1.68</v>
-      </c>
-      <c r="AE3">
-        <v>0</v>
-      </c>
-      <c r="AF3">
-        <v>1.68</v>
-      </c>
-      <c r="AG3">
-        <v>1.677</v>
-      </c>
-      <c r="AH3">
-        <v>0.7407407407407408</v>
-      </c>
-      <c r="AI3">
-        <v>-27.99999999999998</v>
-      </c>
-      <c r="AJ3">
-        <v>0.7403973509933774</v>
-      </c>
-      <c r="AK3">
-        <v>-26.61904761904764</v>
-      </c>
-      <c r="AL3">
-        <v>0.156</v>
-      </c>
-      <c r="AM3">
-        <v>0.156</v>
-      </c>
-      <c r="AN3">
-        <v>73.04347826086956</v>
-      </c>
-      <c r="AO3">
-        <v>-0.08333333333333333</v>
-      </c>
-      <c r="AP3">
-        <v>72.91304347826087</v>
-      </c>
-      <c r="AQ3">
-        <v>-0.08333333333333333</v>
+        <v>202.366813758099</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>0.02</v>
+      </c>
+      <c r="B4">
+        <v>0.2145542962827258</v>
+      </c>
+      <c r="C4">
+        <v>30.39895180719847</v>
+      </c>
+      <c r="D4">
+        <v>26.41559180719847</v>
+      </c>
+      <c r="E4">
+        <v>0.2846400000000001</v>
+      </c>
+      <c r="F4">
+        <v>0.6166400000000001</v>
+      </c>
+      <c r="G4">
+        <v>4.6</v>
+      </c>
+      <c r="H4">
+        <v>30.5</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>3.25</v>
+      </c>
+      <c r="K4">
+        <v>0.461</v>
+      </c>
+      <c r="L4">
+        <v>2.789</v>
+      </c>
+      <c r="M4">
+        <v>0.02756380800000001</v>
+      </c>
+      <c r="N4">
+        <v>2.761436192</v>
+      </c>
+      <c r="O4">
+        <v>0.4142154288</v>
+      </c>
+      <c r="P4">
+        <v>2.3472207632</v>
+      </c>
+      <c r="Q4">
+        <v>2.8082207632</v>
+      </c>
+      <c r="R4">
+        <v>0.02040816326530612</v>
+      </c>
+      <c r="S4">
+        <v>0.2181575472272712</v>
+      </c>
+      <c r="T4">
+        <v>1.009501311659966</v>
+      </c>
+      <c r="U4">
+        <v>0.0447</v>
+      </c>
+      <c r="V4">
+        <v>0.15</v>
+      </c>
+      <c r="W4">
+        <v>0.037995</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y4">
+        <v>101.1834068790495</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>0.03</v>
+      </c>
+      <c r="B5">
+        <v>0.2142817973414779</v>
+      </c>
+      <c r="C5">
+        <v>30.13165156485397</v>
+      </c>
+      <c r="D5">
+        <v>26.45661156485397</v>
+      </c>
+      <c r="E5">
+        <v>0.5929599999999999</v>
+      </c>
+      <c r="F5">
+        <v>0.92496</v>
+      </c>
+      <c r="G5">
+        <v>4.6</v>
+      </c>
+      <c r="H5">
+        <v>30.5</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>3.25</v>
+      </c>
+      <c r="K5">
+        <v>0.461</v>
+      </c>
+      <c r="L5">
+        <v>2.789</v>
+      </c>
+      <c r="M5">
+        <v>0.04134571200000001</v>
+      </c>
+      <c r="N5">
+        <v>2.747654288</v>
+      </c>
+      <c r="O5">
+        <v>0.4121481432</v>
+      </c>
+      <c r="P5">
+        <v>2.3355061448</v>
+      </c>
+      <c r="Q5">
+        <v>2.7965061448</v>
+      </c>
+      <c r="R5">
+        <v>0.03092783505154639</v>
+      </c>
+      <c r="S5">
+        <v>0.2197339663314205</v>
+      </c>
+      <c r="T5">
+        <v>1.01837407546593</v>
+      </c>
+      <c r="U5">
+        <v>0.0447</v>
+      </c>
+      <c r="V5">
+        <v>0.15</v>
+      </c>
+      <c r="W5">
+        <v>0.037995</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y5">
+        <v>67.455604586033</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>0.04</v>
+      </c>
+      <c r="B6">
+        <v>0.21400929840023</v>
+      </c>
+      <c r="C6">
+        <v>29.86447891665694</v>
+      </c>
+      <c r="D6">
+        <v>26.49775891665695</v>
+      </c>
+      <c r="E6">
+        <v>0.9012800000000001</v>
+      </c>
+      <c r="F6">
+        <v>1.23328</v>
+      </c>
+      <c r="G6">
+        <v>4.6</v>
+      </c>
+      <c r="H6">
+        <v>30.5</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>3.25</v>
+      </c>
+      <c r="K6">
+        <v>0.461</v>
+      </c>
+      <c r="L6">
+        <v>2.789</v>
+      </c>
+      <c r="M6">
+        <v>0.05512761600000001</v>
+      </c>
+      <c r="N6">
+        <v>2.733872384</v>
+      </c>
+      <c r="O6">
+        <v>0.4100808576</v>
+      </c>
+      <c r="P6">
+        <v>2.3237915264</v>
+      </c>
+      <c r="Q6">
+        <v>2.7847915264</v>
+      </c>
+      <c r="R6">
+        <v>0.04166666666666667</v>
+      </c>
+      <c r="S6">
+        <v>0.2213432275002396</v>
+      </c>
+      <c r="T6">
+        <v>1.027431688517851</v>
+      </c>
+      <c r="U6">
+        <v>0.0447</v>
+      </c>
+      <c r="V6">
+        <v>0.15</v>
+      </c>
+      <c r="W6">
+        <v>0.037995</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y6">
+        <v>50.59170343952475</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>0.05</v>
+      </c>
+      <c r="B7">
+        <v>0.2137367994589823</v>
+      </c>
+      <c r="C7">
+        <v>29.59743445886739</v>
+      </c>
+      <c r="D7">
+        <v>26.53903445886738</v>
+      </c>
+      <c r="E7">
+        <v>1.2096</v>
+      </c>
+      <c r="F7">
+        <v>1.5416</v>
+      </c>
+      <c r="G7">
+        <v>4.6</v>
+      </c>
+      <c r="H7">
+        <v>30.5</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>3.25</v>
+      </c>
+      <c r="K7">
+        <v>0.461</v>
+      </c>
+      <c r="L7">
+        <v>2.789</v>
+      </c>
+      <c r="M7">
+        <v>0.06890952000000002</v>
+      </c>
+      <c r="N7">
+        <v>2.72009048</v>
+      </c>
+      <c r="O7">
+        <v>0.408013572</v>
+      </c>
+      <c r="P7">
+        <v>2.312076908</v>
+      </c>
+      <c r="Q7">
+        <v>2.773076908</v>
+      </c>
+      <c r="R7">
+        <v>0.05263157894736843</v>
+      </c>
+      <c r="S7">
+        <v>0.2229863678515603</v>
+      </c>
+      <c r="T7">
+        <v>1.03667998816034</v>
+      </c>
+      <c r="U7">
+        <v>0.0447</v>
+      </c>
+      <c r="V7">
+        <v>0.15</v>
+      </c>
+      <c r="W7">
+        <v>0.037995</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y7">
+        <v>40.4733627516198</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>0.06</v>
+      </c>
+      <c r="B8">
+        <v>0.2134643005177344</v>
+      </c>
+      <c r="C8">
+        <v>29.33051879146623</v>
+      </c>
+      <c r="D8">
+        <v>26.58043879146623</v>
+      </c>
+      <c r="E8">
+        <v>1.51792</v>
+      </c>
+      <c r="F8">
+        <v>1.84992</v>
+      </c>
+      <c r="G8">
+        <v>4.6</v>
+      </c>
+      <c r="H8">
+        <v>30.5</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>3.25</v>
+      </c>
+      <c r="K8">
+        <v>0.461</v>
+      </c>
+      <c r="L8">
+        <v>2.789</v>
+      </c>
+      <c r="M8">
+        <v>0.08269142400000001</v>
+      </c>
+      <c r="N8">
+        <v>2.706308576</v>
+      </c>
+      <c r="O8">
+        <v>0.4059462864</v>
+      </c>
+      <c r="P8">
+        <v>2.3003622896</v>
+      </c>
+      <c r="Q8">
+        <v>2.7613622896</v>
+      </c>
+      <c r="R8">
+        <v>0.06382978723404255</v>
+      </c>
+      <c r="S8">
+        <v>0.2246644686358877</v>
+      </c>
+      <c r="T8">
+        <v>1.046125060135647</v>
+      </c>
+      <c r="U8">
+        <v>0.0447</v>
+      </c>
+      <c r="V8">
+        <v>0.15</v>
+      </c>
+      <c r="W8">
+        <v>0.037995</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y8">
+        <v>33.7278022930165</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="B9">
+        <v>0.2131918015764866</v>
+      </c>
+      <c r="C9">
+        <v>29.06373251818446</v>
+      </c>
+      <c r="D9">
+        <v>26.62197251818446</v>
+      </c>
+      <c r="E9">
+        <v>1.82624</v>
+      </c>
+      <c r="F9">
+        <v>2.15824</v>
+      </c>
+      <c r="G9">
+        <v>4.6</v>
+      </c>
+      <c r="H9">
+        <v>30.5</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>3.25</v>
+      </c>
+      <c r="K9">
+        <v>0.461</v>
+      </c>
+      <c r="L9">
+        <v>2.789</v>
+      </c>
+      <c r="M9">
+        <v>0.09647332800000001</v>
+      </c>
+      <c r="N9">
+        <v>2.692526672</v>
+      </c>
+      <c r="O9">
+        <v>0.4038790008</v>
+      </c>
+      <c r="P9">
+        <v>2.2886476712</v>
+      </c>
+      <c r="Q9">
+        <v>2.7496476712</v>
+      </c>
+      <c r="R9">
+        <v>0.07526881720430109</v>
+      </c>
+      <c r="S9">
+        <v>0.2263786576091253</v>
+      </c>
+      <c r="T9">
+        <v>1.05577325193838</v>
+      </c>
+      <c r="U9">
+        <v>0.0447</v>
+      </c>
+      <c r="V9">
+        <v>0.15</v>
+      </c>
+      <c r="W9">
+        <v>0.037995</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y9">
+        <v>28.90954482258557</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>0.08</v>
+      </c>
+      <c r="B10">
+        <v>0.2129193026352388</v>
+      </c>
+      <c r="C10">
+        <v>28.79707624653243</v>
+      </c>
+      <c r="D10">
+        <v>26.66363624653243</v>
+      </c>
+      <c r="E10">
+        <v>2.13456</v>
+      </c>
+      <c r="F10">
+        <v>2.46656</v>
+      </c>
+      <c r="G10">
+        <v>4.6</v>
+      </c>
+      <c r="H10">
+        <v>30.5</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>3.25</v>
+      </c>
+      <c r="K10">
+        <v>0.461</v>
+      </c>
+      <c r="L10">
+        <v>2.789</v>
+      </c>
+      <c r="M10">
+        <v>0.110255232</v>
+      </c>
+      <c r="N10">
+        <v>2.678744768</v>
+      </c>
+      <c r="O10">
+        <v>0.4018117152</v>
+      </c>
+      <c r="P10">
+        <v>2.2769330528</v>
+      </c>
+      <c r="Q10">
+        <v>2.7379330528</v>
+      </c>
+      <c r="R10">
+        <v>0.08695652173913043</v>
+      </c>
+      <c r="S10">
+        <v>0.2281301115600421</v>
+      </c>
+      <c r="T10">
+        <v>1.065631187041173</v>
+      </c>
+      <c r="U10">
+        <v>0.0447</v>
+      </c>
+      <c r="V10">
+        <v>0.15</v>
+      </c>
+      <c r="W10">
+        <v>0.037995</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y10">
+        <v>25.29585171976237</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>0.09</v>
+      </c>
+      <c r="B11">
+        <v>0.2126468036939909</v>
+      </c>
+      <c r="C11">
+        <v>28.53055058782954</v>
+      </c>
+      <c r="D11">
+        <v>26.70543058782954</v>
+      </c>
+      <c r="E11">
+        <v>2.44288</v>
+      </c>
+      <c r="F11">
+        <v>2.77488</v>
+      </c>
+      <c r="G11">
+        <v>4.6</v>
+      </c>
+      <c r="H11">
+        <v>30.5</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>3.25</v>
+      </c>
+      <c r="K11">
+        <v>0.461</v>
+      </c>
+      <c r="L11">
+        <v>2.789</v>
+      </c>
+      <c r="M11">
+        <v>0.124037136</v>
+      </c>
+      <c r="N11">
+        <v>2.664962864</v>
+      </c>
+      <c r="O11">
+        <v>0.3997444296</v>
+      </c>
+      <c r="P11">
+        <v>2.2652184344</v>
+      </c>
+      <c r="Q11">
+        <v>2.7262184344</v>
+      </c>
+      <c r="R11">
+        <v>0.0989010989010989</v>
+      </c>
+      <c r="S11">
+        <v>0.2299200590043856</v>
+      </c>
+      <c r="T11">
+        <v>1.075705780058313</v>
+      </c>
+      <c r="U11">
+        <v>0.0447</v>
+      </c>
+      <c r="V11">
+        <v>0.15</v>
+      </c>
+      <c r="W11">
+        <v>0.037995</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y11">
+        <v>22.48520152867767</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>0.1</v>
+      </c>
+      <c r="B12">
+        <v>0.2123743047527431</v>
+      </c>
+      <c r="C12">
+        <v>28.26415615723404</v>
+      </c>
+      <c r="D12">
+        <v>26.74735615723405</v>
+      </c>
+      <c r="E12">
+        <v>2.7512</v>
+      </c>
+      <c r="F12">
+        <v>3.0832</v>
+      </c>
+      <c r="G12">
+        <v>4.6</v>
+      </c>
+      <c r="H12">
+        <v>30.5</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>3.25</v>
+      </c>
+      <c r="K12">
+        <v>0.461</v>
+      </c>
+      <c r="L12">
+        <v>2.789</v>
+      </c>
+      <c r="M12">
+        <v>0.13781904</v>
+      </c>
+      <c r="N12">
+        <v>2.65118096</v>
+      </c>
+      <c r="O12">
+        <v>0.397677144</v>
+      </c>
+      <c r="P12">
+        <v>2.253503816</v>
+      </c>
+      <c r="Q12">
+        <v>2.714503816</v>
+      </c>
+      <c r="R12">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="S12">
+        <v>0.2317497830586035</v>
+      </c>
+      <c r="T12">
+        <v>1.086004252920278</v>
+      </c>
+      <c r="U12">
+        <v>0.0447</v>
+      </c>
+      <c r="V12">
+        <v>0.15</v>
+      </c>
+      <c r="W12">
+        <v>0.037995</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y12">
+        <v>20.2366813758099</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>0.11</v>
+      </c>
+      <c r="B13">
+        <v>0.2121018058114953</v>
+      </c>
+      <c r="C13">
+        <v>27.99789357377334</v>
+      </c>
+      <c r="D13">
+        <v>26.78941357377334</v>
+      </c>
+      <c r="E13">
+        <v>3.05952</v>
+      </c>
+      <c r="F13">
+        <v>3.39152</v>
+      </c>
+      <c r="G13">
+        <v>4.6</v>
+      </c>
+      <c r="H13">
+        <v>30.5</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>3.25</v>
+      </c>
+      <c r="K13">
+        <v>0.461</v>
+      </c>
+      <c r="L13">
+        <v>2.789</v>
+      </c>
+      <c r="M13">
+        <v>0.151600944</v>
+      </c>
+      <c r="N13">
+        <v>2.637399056</v>
+      </c>
+      <c r="O13">
+        <v>0.3956098584</v>
+      </c>
+      <c r="P13">
+        <v>2.2417891976</v>
+      </c>
+      <c r="Q13">
+        <v>2.7027891976</v>
+      </c>
+      <c r="R13">
+        <v>0.1235955056179775</v>
+      </c>
+      <c r="S13">
+        <v>0.233620624507298</v>
+      </c>
+      <c r="T13">
+        <v>1.096534152138691</v>
+      </c>
+      <c r="U13">
+        <v>0.0447</v>
+      </c>
+      <c r="V13">
+        <v>0.15</v>
+      </c>
+      <c r="W13">
+        <v>0.037995</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y13">
+        <v>18.39698306891809</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>0.12</v>
+      </c>
+      <c r="B14">
+        <v>0.2118293068702475</v>
+      </c>
+      <c r="C14">
+        <v>27.73176346037432</v>
+      </c>
+      <c r="D14">
+        <v>26.83160346037433</v>
+      </c>
+      <c r="E14">
+        <v>3.36784</v>
+      </c>
+      <c r="F14">
+        <v>3.69984</v>
+      </c>
+      <c r="G14">
+        <v>4.6</v>
+      </c>
+      <c r="H14">
+        <v>30.5</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>3.25</v>
+      </c>
+      <c r="K14">
+        <v>0.461</v>
+      </c>
+      <c r="L14">
+        <v>2.789</v>
+      </c>
+      <c r="M14">
+        <v>0.165382848</v>
+      </c>
+      <c r="N14">
+        <v>2.623617152</v>
+      </c>
+      <c r="O14">
+        <v>0.3935425728</v>
+      </c>
+      <c r="P14">
+        <v>2.2300745792</v>
+      </c>
+      <c r="Q14">
+        <v>2.6910745792</v>
+      </c>
+      <c r="R14">
+        <v>0.1363636363636364</v>
+      </c>
+      <c r="S14">
+        <v>0.2355339850798266</v>
+      </c>
+      <c r="T14">
+        <v>1.107303367248433</v>
+      </c>
+      <c r="U14">
+        <v>0.0447</v>
+      </c>
+      <c r="V14">
+        <v>0.15</v>
+      </c>
+      <c r="W14">
+        <v>0.037995</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y14">
+        <v>16.86390114650825</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>0.13</v>
+      </c>
+      <c r="B15">
+        <v>0.2115568079289996</v>
+      </c>
+      <c r="C15">
+        <v>27.46576644389426</v>
+      </c>
+      <c r="D15">
+        <v>26.87392644389426</v>
+      </c>
+      <c r="E15">
+        <v>3.67616</v>
+      </c>
+      <c r="F15">
+        <v>4.00816</v>
+      </c>
+      <c r="G15">
+        <v>4.6</v>
+      </c>
+      <c r="H15">
+        <v>30.5</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>3.25</v>
+      </c>
+      <c r="K15">
+        <v>0.461</v>
+      </c>
+      <c r="L15">
+        <v>2.789</v>
+      </c>
+      <c r="M15">
+        <v>0.179164752</v>
+      </c>
+      <c r="N15">
+        <v>2.609835248</v>
+      </c>
+      <c r="O15">
+        <v>0.3914752872</v>
+      </c>
+      <c r="P15">
+        <v>2.2183599608</v>
+      </c>
+      <c r="Q15">
+        <v>2.6793599608</v>
+      </c>
+      <c r="R15">
+        <v>0.1494252873563219</v>
+      </c>
+      <c r="S15">
+        <v>0.2374913309528731</v>
+      </c>
+      <c r="T15">
+        <v>1.118320150521616</v>
+      </c>
+      <c r="U15">
+        <v>0.0447</v>
+      </c>
+      <c r="V15">
+        <v>0.15</v>
+      </c>
+      <c r="W15">
+        <v>0.037995</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y15">
+        <v>15.56667798139223</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>0.14</v>
+      </c>
+      <c r="B16">
+        <v>0.2112843089877517</v>
+      </c>
+      <c r="C16">
+        <v>27.19990315515171</v>
+      </c>
+      <c r="D16">
+        <v>26.91638315515171</v>
+      </c>
+      <c r="E16">
+        <v>3.98448</v>
+      </c>
+      <c r="F16">
+        <v>4.31648</v>
+      </c>
+      <c r="G16">
+        <v>4.6</v>
+      </c>
+      <c r="H16">
+        <v>30.5</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>3.25</v>
+      </c>
+      <c r="K16">
+        <v>0.461</v>
+      </c>
+      <c r="L16">
+        <v>2.789</v>
+      </c>
+      <c r="M16">
+        <v>0.192946656</v>
+      </c>
+      <c r="N16">
+        <v>2.596053344</v>
+      </c>
+      <c r="O16">
+        <v>0.3894080016</v>
+      </c>
+      <c r="P16">
+        <v>2.2066453424</v>
+      </c>
+      <c r="Q16">
+        <v>2.6676453424</v>
+      </c>
+      <c r="R16">
+        <v>0.1627906976744186</v>
+      </c>
+      <c r="S16">
+        <v>0.2394941964973858</v>
+      </c>
+      <c r="T16">
+        <v>1.129593138056967</v>
+      </c>
+      <c r="U16">
+        <v>0.0447</v>
+      </c>
+      <c r="V16">
+        <v>0.15</v>
+      </c>
+      <c r="W16">
+        <v>0.037995</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y16">
+        <v>14.45477241129279</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>0.15</v>
+      </c>
+      <c r="B17">
+        <v>0.2110118100465039</v>
+      </c>
+      <c r="C17">
+        <v>26.93417422895796</v>
+      </c>
+      <c r="D17">
+        <v>26.95897422895797</v>
+      </c>
+      <c r="E17">
+        <v>4.2928</v>
+      </c>
+      <c r="F17">
+        <v>4.6248</v>
+      </c>
+      <c r="G17">
+        <v>4.6</v>
+      </c>
+      <c r="H17">
+        <v>30.5</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>3.25</v>
+      </c>
+      <c r="K17">
+        <v>0.461</v>
+      </c>
+      <c r="L17">
+        <v>2.789</v>
+      </c>
+      <c r="M17">
+        <v>0.20672856</v>
+      </c>
+      <c r="N17">
+        <v>2.58227144</v>
+      </c>
+      <c r="O17">
+        <v>0.387340716</v>
+      </c>
+      <c r="P17">
+        <v>2.194930724</v>
+      </c>
+      <c r="Q17">
+        <v>2.655930724</v>
+      </c>
+      <c r="R17">
+        <v>0.1764705882352941</v>
+      </c>
+      <c r="S17">
+        <v>0.2415441882900046</v>
+      </c>
+      <c r="T17">
+        <v>1.141131372357855</v>
+      </c>
+      <c r="U17">
+        <v>0.0447</v>
+      </c>
+      <c r="V17">
+        <v>0.15</v>
+      </c>
+      <c r="W17">
+        <v>0.037995</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y17">
+        <v>13.4911209172066</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>0.16</v>
+      </c>
+      <c r="B18">
+        <v>0.2108889111052561</v>
+      </c>
+      <c r="C18">
+        <v>26.64510723816458</v>
+      </c>
+      <c r="D18">
+        <v>26.97822723816459</v>
+      </c>
+      <c r="E18">
+        <v>4.601120000000001</v>
+      </c>
+      <c r="F18">
+        <v>4.933120000000001</v>
+      </c>
+      <c r="G18">
+        <v>4.6</v>
+      </c>
+      <c r="H18">
+        <v>30.5</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>3.25</v>
+      </c>
+      <c r="K18">
+        <v>0.461</v>
+      </c>
+      <c r="L18">
+        <v>2.789</v>
+      </c>
+      <c r="M18">
+        <v>0.225936896</v>
+      </c>
+      <c r="N18">
+        <v>2.563063104</v>
+      </c>
+      <c r="O18">
+        <v>0.3844594656</v>
+      </c>
+      <c r="P18">
+        <v>2.1786036384</v>
+      </c>
+      <c r="Q18">
+        <v>2.6396036384</v>
+      </c>
+      <c r="R18">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="S18">
+        <v>0.2436429894110191</v>
+      </c>
+      <c r="T18">
+        <v>1.15294432652305</v>
+      </c>
+      <c r="U18">
+        <v>0.0458</v>
+      </c>
+      <c r="V18">
+        <v>0.15</v>
+      </c>
+      <c r="W18">
+        <v>0.03893</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y18">
+        <v>12.34415471477487</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>0.17</v>
+      </c>
+      <c r="B19">
+        <v>0.2106257621640082</v>
+      </c>
+      <c r="C19">
+        <v>26.37810404563895</v>
+      </c>
+      <c r="D19">
+        <v>27.01954404563896</v>
+      </c>
+      <c r="E19">
+        <v>4.909440000000001</v>
+      </c>
+      <c r="F19">
+        <v>5.241440000000001</v>
+      </c>
+      <c r="G19">
+        <v>4.6</v>
+      </c>
+      <c r="H19">
+        <v>30.5</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>3.25</v>
+      </c>
+      <c r="K19">
+        <v>0.461</v>
+      </c>
+      <c r="L19">
+        <v>2.789</v>
+      </c>
+      <c r="M19">
+        <v>0.240057952</v>
+      </c>
+      <c r="N19">
+        <v>2.548942048</v>
+      </c>
+      <c r="O19">
+        <v>0.3823413072</v>
+      </c>
+      <c r="P19">
+        <v>2.1666007408</v>
+      </c>
+      <c r="Q19">
+        <v>2.6276007408</v>
+      </c>
+      <c r="R19">
+        <v>0.2048192771084338</v>
+      </c>
+      <c r="S19">
+        <v>0.245792364053022</v>
+      </c>
+      <c r="T19">
+        <v>1.165041930186202</v>
+      </c>
+      <c r="U19">
+        <v>0.0458</v>
+      </c>
+      <c r="V19">
+        <v>0.15</v>
+      </c>
+      <c r="W19">
+        <v>0.03893</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y19">
+        <v>11.61802796684694</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>0.18</v>
+      </c>
+      <c r="B20">
+        <v>0.2103626132227605</v>
+      </c>
+      <c r="C20">
+        <v>26.11122759954061</v>
+      </c>
+      <c r="D20">
+        <v>27.06098759954061</v>
+      </c>
+      <c r="E20">
+        <v>5.21776</v>
+      </c>
+      <c r="F20">
+        <v>5.54976</v>
+      </c>
+      <c r="G20">
+        <v>4.6</v>
+      </c>
+      <c r="H20">
+        <v>30.5</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>3.25</v>
+      </c>
+      <c r="K20">
+        <v>0.461</v>
+      </c>
+      <c r="L20">
+        <v>2.789</v>
+      </c>
+      <c r="M20">
+        <v>0.254179008</v>
+      </c>
+      <c r="N20">
+        <v>2.534820992</v>
+      </c>
+      <c r="O20">
+        <v>0.3802231488</v>
+      </c>
+      <c r="P20">
+        <v>2.1545978432</v>
+      </c>
+      <c r="Q20">
+        <v>2.6155978432</v>
+      </c>
+      <c r="R20">
+        <v>0.2195121951219512</v>
+      </c>
+      <c r="S20">
+        <v>0.247994162466781</v>
+      </c>
+      <c r="T20">
+        <v>1.177434597353333</v>
+      </c>
+      <c r="U20">
+        <v>0.0458</v>
+      </c>
+      <c r="V20">
+        <v>0.15</v>
+      </c>
+      <c r="W20">
+        <v>0.03893</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y20">
+        <v>10.97258196868878</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>0.19</v>
+      </c>
+      <c r="B21">
+        <v>0.2100994642815126</v>
+      </c>
+      <c r="C21">
+        <v>25.8444784839903</v>
+      </c>
+      <c r="D21">
+        <v>27.1025584839903</v>
+      </c>
+      <c r="E21">
+        <v>5.52608</v>
+      </c>
+      <c r="F21">
+        <v>5.85808</v>
+      </c>
+      <c r="G21">
+        <v>4.6</v>
+      </c>
+      <c r="H21">
+        <v>30.5</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>3.25</v>
+      </c>
+      <c r="K21">
+        <v>0.461</v>
+      </c>
+      <c r="L21">
+        <v>2.789</v>
+      </c>
+      <c r="M21">
+        <v>0.268300064</v>
+      </c>
+      <c r="N21">
+        <v>2.520699936</v>
+      </c>
+      <c r="O21">
+        <v>0.3781049904</v>
+      </c>
+      <c r="P21">
+        <v>2.1425949456</v>
+      </c>
+      <c r="Q21">
+        <v>2.6035949456</v>
+      </c>
+      <c r="R21">
+        <v>0.2345679012345679</v>
+      </c>
+      <c r="S21">
+        <v>0.2502503262734723</v>
+      </c>
+      <c r="T21">
+        <v>1.190133256302369</v>
+      </c>
+      <c r="U21">
+        <v>0.0458</v>
+      </c>
+      <c r="V21">
+        <v>0.15</v>
+      </c>
+      <c r="W21">
+        <v>0.03893</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y21">
+        <v>10.39507765454726</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>0.2</v>
+      </c>
+      <c r="B22">
+        <v>0.2102103153402648</v>
+      </c>
+      <c r="C22">
+        <v>25.51863125818199</v>
+      </c>
+      <c r="D22">
+        <v>27.08503125818199</v>
+      </c>
+      <c r="E22">
+        <v>5.8344</v>
+      </c>
+      <c r="F22">
+        <v>6.1664</v>
+      </c>
+      <c r="G22">
+        <v>4.6</v>
+      </c>
+      <c r="H22">
+        <v>30.5</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>3.25</v>
+      </c>
+      <c r="K22">
+        <v>0.461</v>
+      </c>
+      <c r="L22">
+        <v>2.789</v>
+      </c>
+      <c r="M22">
+        <v>0.2959872</v>
+      </c>
+      <c r="N22">
+        <v>2.4930128</v>
+      </c>
+      <c r="O22">
+        <v>0.37395192</v>
+      </c>
+      <c r="P22">
+        <v>2.11906088</v>
+      </c>
+      <c r="Q22">
+        <v>2.58006088</v>
+      </c>
+      <c r="R22">
+        <v>0.25</v>
+      </c>
+      <c r="S22">
+        <v>0.252562894175331</v>
+      </c>
+      <c r="T22">
+        <v>1.20314938172513</v>
+      </c>
+      <c r="U22">
+        <v>0.048</v>
+      </c>
+      <c r="V22">
+        <v>0.15</v>
+      </c>
+      <c r="W22">
+        <v>0.0408</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y22">
+        <v>9.422704765611487</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>0.21</v>
+      </c>
+      <c r="B23">
+        <v>0.2099658663990169</v>
+      </c>
+      <c r="C23">
+        <v>25.24899249383964</v>
+      </c>
+      <c r="D23">
+        <v>27.12371249383964</v>
+      </c>
+      <c r="E23">
+        <v>6.14272</v>
+      </c>
+      <c r="F23">
+        <v>6.47472</v>
+      </c>
+      <c r="G23">
+        <v>4.6</v>
+      </c>
+      <c r="H23">
+        <v>30.5</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>3.25</v>
+      </c>
+      <c r="K23">
+        <v>0.461</v>
+      </c>
+      <c r="L23">
+        <v>2.789</v>
+      </c>
+      <c r="M23">
+        <v>0.31078656</v>
+      </c>
+      <c r="N23">
+        <v>2.47821344</v>
+      </c>
+      <c r="O23">
+        <v>0.371732016</v>
+      </c>
+      <c r="P23">
+        <v>2.106481424</v>
+      </c>
+      <c r="Q23">
+        <v>2.567481424</v>
+      </c>
+      <c r="R23">
+        <v>0.2658227848101266</v>
+      </c>
+      <c r="S23">
+        <v>0.2549340081000214</v>
+      </c>
+      <c r="T23">
+        <v>1.216495029310493</v>
+      </c>
+      <c r="U23">
+        <v>0.048</v>
+      </c>
+      <c r="V23">
+        <v>0.15</v>
+      </c>
+      <c r="W23">
+        <v>0.0408</v>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y23">
+        <v>8.974004538677606</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>0.22</v>
+      </c>
+      <c r="B24">
+        <v>0.2097214174577691</v>
+      </c>
+      <c r="C24">
+        <v>24.97946437200476</v>
+      </c>
+      <c r="D24">
+        <v>27.16250437200475</v>
+      </c>
+      <c r="E24">
+        <v>6.451040000000001</v>
+      </c>
+      <c r="F24">
+        <v>6.783040000000001</v>
+      </c>
+      <c r="G24">
+        <v>4.6</v>
+      </c>
+      <c r="H24">
+        <v>30.5</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>3.25</v>
+      </c>
+      <c r="K24">
+        <v>0.461</v>
+      </c>
+      <c r="L24">
+        <v>2.789</v>
+      </c>
+      <c r="M24">
+        <v>0.32558592</v>
+      </c>
+      <c r="N24">
+        <v>2.46341408</v>
+      </c>
+      <c r="O24">
+        <v>0.369512112</v>
+      </c>
+      <c r="P24">
+        <v>2.093901968</v>
+      </c>
+      <c r="Q24">
+        <v>2.554901968</v>
+      </c>
+      <c r="R24">
+        <v>0.282051282051282</v>
+      </c>
+      <c r="S24">
+        <v>0.2573659198176527</v>
+      </c>
+      <c r="T24">
+        <v>1.230182872987788</v>
+      </c>
+      <c r="U24">
+        <v>0.048</v>
+      </c>
+      <c r="V24">
+        <v>0.15</v>
+      </c>
+      <c r="W24">
+        <v>0.0408</v>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y24">
+        <v>8.566095241464987</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>0.23</v>
+      </c>
+      <c r="B25">
+        <v>0.2094769685165213</v>
+      </c>
+      <c r="C25">
+        <v>24.71004736807438</v>
+      </c>
+      <c r="D25">
+        <v>27.20140736807439</v>
+      </c>
+      <c r="E25">
+        <v>6.759360000000001</v>
+      </c>
+      <c r="F25">
+        <v>7.091360000000001</v>
+      </c>
+      <c r="G25">
+        <v>4.6</v>
+      </c>
+      <c r="H25">
+        <v>30.5</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>3.25</v>
+      </c>
+      <c r="K25">
+        <v>0.461</v>
+      </c>
+      <c r="L25">
+        <v>2.789</v>
+      </c>
+      <c r="M25">
+        <v>0.3403852800000001</v>
+      </c>
+      <c r="N25">
+        <v>2.44861472</v>
+      </c>
+      <c r="O25">
+        <v>0.367292208</v>
+      </c>
+      <c r="P25">
+        <v>2.081322512</v>
+      </c>
+      <c r="Q25">
+        <v>2.542322512</v>
+      </c>
+      <c r="R25">
+        <v>0.2987012987012987</v>
+      </c>
+      <c r="S25">
+        <v>0.2598609980734042</v>
+      </c>
+      <c r="T25">
+        <v>1.244226245072286</v>
+      </c>
+      <c r="U25">
+        <v>0.048</v>
+      </c>
+      <c r="V25">
+        <v>0.15</v>
+      </c>
+      <c r="W25">
+        <v>0.0408</v>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y25">
+        <v>8.193656317923029</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>0.24</v>
+      </c>
+      <c r="B26">
+        <v>0.2092325195752734</v>
+      </c>
+      <c r="C26">
+        <v>24.44074196017306</v>
+      </c>
+      <c r="D26">
+        <v>27.24042196017306</v>
+      </c>
+      <c r="E26">
+        <v>7.06768</v>
+      </c>
+      <c r="F26">
+        <v>7.39968</v>
+      </c>
+      <c r="G26">
+        <v>4.6</v>
+      </c>
+      <c r="H26">
+        <v>30.5</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>3.25</v>
+      </c>
+      <c r="K26">
+        <v>0.461</v>
+      </c>
+      <c r="L26">
+        <v>2.789</v>
+      </c>
+      <c r="M26">
+        <v>0.35518464</v>
+      </c>
+      <c r="N26">
+        <v>2.43381536</v>
+      </c>
+      <c r="O26">
+        <v>0.365072304</v>
+      </c>
+      <c r="P26">
+        <v>2.068743056</v>
+      </c>
+      <c r="Q26">
+        <v>2.529743056</v>
+      </c>
+      <c r="R26">
+        <v>0.3157894736842105</v>
+      </c>
+      <c r="S26">
+        <v>0.2624217362832545</v>
+      </c>
+      <c r="T26">
+        <v>1.25863917958006</v>
+      </c>
+      <c r="U26">
+        <v>0.048</v>
+      </c>
+      <c r="V26">
+        <v>0.15</v>
+      </c>
+      <c r="W26">
+        <v>0.0408</v>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y26">
+        <v>7.852253971342905</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>0.25</v>
+      </c>
+      <c r="B27">
+        <v>0.2093068206340256</v>
+      </c>
+      <c r="C27">
+        <v>24.12055151308495</v>
+      </c>
+      <c r="D27">
+        <v>27.22855151308496</v>
+      </c>
+      <c r="E27">
+        <v>7.376</v>
+      </c>
+      <c r="F27">
+        <v>7.708</v>
+      </c>
+      <c r="G27">
+        <v>4.6</v>
+      </c>
+      <c r="H27">
+        <v>30.5</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>3.25</v>
+      </c>
+      <c r="K27">
+        <v>0.461</v>
+      </c>
+      <c r="L27">
+        <v>2.789</v>
+      </c>
+      <c r="M27">
+        <v>0.3815460000000001</v>
+      </c>
+      <c r="N27">
+        <v>2.407454</v>
+      </c>
+      <c r="O27">
+        <v>0.3611181</v>
+      </c>
+      <c r="P27">
+        <v>2.0463359</v>
+      </c>
+      <c r="Q27">
+        <v>2.5073359</v>
+      </c>
+      <c r="R27">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="S27">
+        <v>0.2650507608453674</v>
+      </c>
+      <c r="T27">
+        <v>1.273436459008041</v>
+      </c>
+      <c r="U27">
+        <v>0.0495</v>
+      </c>
+      <c r="V27">
+        <v>0.15</v>
+      </c>
+      <c r="W27">
+        <v>0.042075</v>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y27">
+        <v>7.309734606050122</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>0.26</v>
+      </c>
+      <c r="B28">
+        <v>0.2090751216927778</v>
+      </c>
+      <c r="C28">
+        <v>23.84928229592731</v>
+      </c>
+      <c r="D28">
+        <v>27.26560229592731</v>
+      </c>
+      <c r="E28">
+        <v>7.68432</v>
+      </c>
+      <c r="F28">
+        <v>8.01632</v>
+      </c>
+      <c r="G28">
+        <v>4.6</v>
+      </c>
+      <c r="H28">
+        <v>30.5</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>3.25</v>
+      </c>
+      <c r="K28">
+        <v>0.461</v>
+      </c>
+      <c r="L28">
+        <v>2.789</v>
+      </c>
+      <c r="M28">
+        <v>0.39680784</v>
+      </c>
+      <c r="N28">
+        <v>2.39219216</v>
+      </c>
+      <c r="O28">
+        <v>0.358828824</v>
+      </c>
+      <c r="P28">
+        <v>2.033363336</v>
+      </c>
+      <c r="Q28">
+        <v>2.494363336</v>
+      </c>
+      <c r="R28">
+        <v>0.3513513513513514</v>
+      </c>
+      <c r="S28">
+        <v>0.2677508401253754</v>
+      </c>
+      <c r="T28">
+        <v>1.288633664907049</v>
+      </c>
+      <c r="U28">
+        <v>0.0495</v>
+      </c>
+      <c r="V28">
+        <v>0.15</v>
+      </c>
+      <c r="W28">
+        <v>0.042075</v>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y28">
+        <v>7.028590967355886</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>0.27</v>
+      </c>
+      <c r="B29">
+        <v>0.2088434227515299</v>
+      </c>
+      <c r="C29">
+        <v>23.57811404859275</v>
+      </c>
+      <c r="D29">
+        <v>27.30275404859276</v>
+      </c>
+      <c r="E29">
+        <v>7.992640000000001</v>
+      </c>
+      <c r="F29">
+        <v>8.32464</v>
+      </c>
+      <c r="G29">
+        <v>4.6</v>
+      </c>
+      <c r="H29">
+        <v>30.5</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>3.25</v>
+      </c>
+      <c r="K29">
+        <v>0.461</v>
+      </c>
+      <c r="L29">
+        <v>2.789</v>
+      </c>
+      <c r="M29">
+        <v>0.41206968</v>
+      </c>
+      <c r="N29">
+        <v>2.37693032</v>
+      </c>
+      <c r="O29">
+        <v>0.356539548</v>
+      </c>
+      <c r="P29">
+        <v>2.020390772</v>
+      </c>
+      <c r="Q29">
+        <v>2.481390772</v>
+      </c>
+      <c r="R29">
+        <v>0.3698630136986302</v>
+      </c>
+      <c r="S29">
+        <v>0.270524894180178</v>
+      </c>
+      <c r="T29">
+        <v>1.304247232611509</v>
+      </c>
+      <c r="U29">
+        <v>0.0495</v>
+      </c>
+      <c r="V29">
+        <v>0.15</v>
+      </c>
+      <c r="W29">
+        <v>0.042075</v>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y29">
+        <v>6.768272783379742</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>0.28</v>
+      </c>
+      <c r="B30">
+        <v>0.2086117238102821</v>
+      </c>
+      <c r="C30">
+        <v>23.30704718438493</v>
+      </c>
+      <c r="D30">
+        <v>27.34000718438493</v>
+      </c>
+      <c r="E30">
+        <v>8.30096</v>
+      </c>
+      <c r="F30">
+        <v>8.632960000000001</v>
+      </c>
+      <c r="G30">
+        <v>4.6</v>
+      </c>
+      <c r="H30">
+        <v>30.5</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>3.25</v>
+      </c>
+      <c r="K30">
+        <v>0.461</v>
+      </c>
+      <c r="L30">
+        <v>2.789</v>
+      </c>
+      <c r="M30">
+        <v>0.4273315200000001</v>
+      </c>
+      <c r="N30">
+        <v>2.36166848</v>
+      </c>
+      <c r="O30">
+        <v>0.354250272</v>
+      </c>
+      <c r="P30">
+        <v>2.007418208</v>
+      </c>
+      <c r="Q30">
+        <v>2.468418208</v>
+      </c>
+      <c r="R30">
+        <v>0.388888888888889</v>
+      </c>
+      <c r="S30">
+        <v>0.2733760052920585</v>
+      </c>
+      <c r="T30">
+        <v>1.320294510529982</v>
+      </c>
+      <c r="U30">
+        <v>0.0495</v>
+      </c>
+      <c r="V30">
+        <v>0.15</v>
+      </c>
+      <c r="W30">
+        <v>0.042075</v>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y30">
+        <v>6.526548755401894</v>
+      </c>
+      <c r="Z30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>0.29</v>
+      </c>
+      <c r="B31">
+        <v>0.2083800248690343</v>
+      </c>
+      <c r="C31">
+        <v>23.0360821188663</v>
+      </c>
+      <c r="D31">
+        <v>27.37736211886629</v>
+      </c>
+      <c r="E31">
+        <v>8.609279999999998</v>
+      </c>
+      <c r="F31">
+        <v>8.941279999999999</v>
+      </c>
+      <c r="G31">
+        <v>4.6</v>
+      </c>
+      <c r="H31">
+        <v>30.5</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>3.25</v>
+      </c>
+      <c r="K31">
+        <v>0.461</v>
+      </c>
+      <c r="L31">
+        <v>2.789</v>
+      </c>
+      <c r="M31">
+        <v>0.44259336</v>
+      </c>
+      <c r="N31">
+        <v>2.34640664</v>
+      </c>
+      <c r="O31">
+        <v>0.351960996</v>
+      </c>
+      <c r="P31">
+        <v>1.994445644</v>
+      </c>
+      <c r="Q31">
+        <v>2.455445644</v>
+      </c>
+      <c r="R31">
+        <v>0.4084507042253521</v>
+      </c>
+      <c r="S31">
+        <v>0.276307429393006</v>
+      </c>
+      <c r="T31">
+        <v>1.336793824446159</v>
+      </c>
+      <c r="U31">
+        <v>0.0495</v>
+      </c>
+      <c r="V31">
+        <v>0.15</v>
+      </c>
+      <c r="W31">
+        <v>0.042075</v>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y31">
+        <v>6.30149535004321</v>
+      </c>
+      <c r="Z31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>0.3</v>
+      </c>
+      <c r="B32">
+        <v>0.2085053259277865</v>
+      </c>
+      <c r="C32">
+        <v>22.70754818367845</v>
+      </c>
+      <c r="D32">
+        <v>27.35714818367845</v>
+      </c>
+      <c r="E32">
+        <v>8.917599999999998</v>
+      </c>
+      <c r="F32">
+        <v>9.249599999999999</v>
+      </c>
+      <c r="G32">
+        <v>4.6</v>
+      </c>
+      <c r="H32">
+        <v>30.5</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>3.25</v>
+      </c>
+      <c r="K32">
+        <v>0.461</v>
+      </c>
+      <c r="L32">
+        <v>2.789</v>
+      </c>
+      <c r="M32">
+        <v>0.4708046399999999</v>
+      </c>
+      <c r="N32">
+        <v>2.31819536</v>
+      </c>
+      <c r="O32">
+        <v>0.347729304</v>
+      </c>
+      <c r="P32">
+        <v>1.970466056</v>
+      </c>
+      <c r="Q32">
+        <v>2.431466056</v>
+      </c>
+      <c r="R32">
+        <v>0.4285714285714286</v>
+      </c>
+      <c r="S32">
+        <v>0.2793226084682664</v>
+      </c>
+      <c r="T32">
+        <v>1.353764547331369</v>
+      </c>
+      <c r="U32">
+        <v>0.0509</v>
+      </c>
+      <c r="V32">
+        <v>0.15</v>
+      </c>
+      <c r="W32">
+        <v>0.043265</v>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y32">
+        <v>5.923900834962035</v>
+      </c>
+      <c r="Z32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>0.31</v>
+      </c>
+      <c r="B33">
+        <v>0.2082855269865386</v>
+      </c>
+      <c r="C33">
+        <v>22.4347065653034</v>
+      </c>
+      <c r="D33">
+        <v>27.3926265653034</v>
+      </c>
+      <c r="E33">
+        <v>9.225919999999999</v>
+      </c>
+      <c r="F33">
+        <v>9.557919999999999</v>
+      </c>
+      <c r="G33">
+        <v>4.6</v>
+      </c>
+      <c r="H33">
+        <v>30.5</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>3.25</v>
+      </c>
+      <c r="K33">
+        <v>0.461</v>
+      </c>
+      <c r="L33">
+        <v>2.789</v>
+      </c>
+      <c r="M33">
+        <v>0.486498128</v>
+      </c>
+      <c r="N33">
+        <v>2.302501872</v>
+      </c>
+      <c r="O33">
+        <v>0.3453752808</v>
+      </c>
+      <c r="P33">
+        <v>1.9571265912</v>
+      </c>
+      <c r="Q33">
+        <v>2.4181265912</v>
+      </c>
+      <c r="R33">
+        <v>0.4492753623188406</v>
+      </c>
+      <c r="S33">
+        <v>0.2824251840384617</v>
+      </c>
+      <c r="T33">
+        <v>1.371227175227744</v>
+      </c>
+      <c r="U33">
+        <v>0.0509</v>
+      </c>
+      <c r="V33">
+        <v>0.15</v>
+      </c>
+      <c r="W33">
+        <v>0.043265</v>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y33">
+        <v>5.732807259640679</v>
+      </c>
+      <c r="Z33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>0.32</v>
+      </c>
+      <c r="B34">
+        <v>0.2080657280452908</v>
+      </c>
+      <c r="C34">
+        <v>22.16195708738475</v>
+      </c>
+      <c r="D34">
+        <v>27.42819708738475</v>
+      </c>
+      <c r="E34">
+        <v>9.53424</v>
+      </c>
+      <c r="F34">
+        <v>9.866240000000001</v>
+      </c>
+      <c r="G34">
+        <v>4.6</v>
+      </c>
+      <c r="H34">
+        <v>30.5</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>3.25</v>
+      </c>
+      <c r="K34">
+        <v>0.461</v>
+      </c>
+      <c r="L34">
+        <v>2.789</v>
+      </c>
+      <c r="M34">
+        <v>0.5021916160000001</v>
+      </c>
+      <c r="N34">
+        <v>2.286808384</v>
+      </c>
+      <c r="O34">
+        <v>0.3430212576</v>
+      </c>
+      <c r="P34">
+        <v>1.9437871264</v>
+      </c>
+      <c r="Q34">
+        <v>2.4047871264</v>
+      </c>
+      <c r="R34">
+        <v>0.4705882352941177</v>
+      </c>
+      <c r="S34">
+        <v>0.28561901183131</v>
+      </c>
+      <c r="T34">
+        <v>1.389203409826954</v>
+      </c>
+      <c r="U34">
+        <v>0.0509</v>
+      </c>
+      <c r="V34">
+        <v>0.15</v>
+      </c>
+      <c r="W34">
+        <v>0.043265</v>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y34">
+        <v>5.553657032776907</v>
+      </c>
+      <c r="Z34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>0.33</v>
+      </c>
+      <c r="B35">
+        <v>0.2078459291040429</v>
+      </c>
+      <c r="C35">
+        <v>21.88930010933444</v>
+      </c>
+      <c r="D35">
+        <v>27.46386010933444</v>
+      </c>
+      <c r="E35">
+        <v>9.842560000000001</v>
+      </c>
+      <c r="F35">
+        <v>10.17456</v>
+      </c>
+      <c r="G35">
+        <v>4.6</v>
+      </c>
+      <c r="H35">
+        <v>30.5</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>3.25</v>
+      </c>
+      <c r="K35">
+        <v>0.461</v>
+      </c>
+      <c r="L35">
+        <v>2.789</v>
+      </c>
+      <c r="M35">
+        <v>0.5178851040000001</v>
+      </c>
+      <c r="N35">
+        <v>2.271114896</v>
+      </c>
+      <c r="O35">
+        <v>0.3406672344</v>
+      </c>
+      <c r="P35">
+        <v>1.9304476616</v>
+      </c>
+      <c r="Q35">
+        <v>2.3914476616</v>
+      </c>
+      <c r="R35">
+        <v>0.4925373134328359</v>
+      </c>
+      <c r="S35">
+        <v>0.2889081777672283</v>
+      </c>
+      <c r="T35">
+        <v>1.407716248444051</v>
+      </c>
+      <c r="U35">
+        <v>0.0509</v>
+      </c>
+      <c r="V35">
+        <v>0.15</v>
+      </c>
+      <c r="W35">
+        <v>0.043265</v>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y35">
+        <v>5.385364395420031</v>
+      </c>
+      <c r="Z35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>0.34</v>
+      </c>
+      <c r="B36">
+        <v>0.2076261301627951</v>
+      </c>
+      <c r="C36">
+        <v>21.61673599243613</v>
+      </c>
+      <c r="D36">
+        <v>27.49961599243613</v>
+      </c>
+      <c r="E36">
+        <v>10.15088</v>
+      </c>
+      <c r="F36">
+        <v>10.48288</v>
+      </c>
+      <c r="G36">
+        <v>4.6</v>
+      </c>
+      <c r="H36">
+        <v>30.5</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>3.25</v>
+      </c>
+      <c r="K36">
+        <v>0.461</v>
+      </c>
+      <c r="L36">
+        <v>2.789</v>
+      </c>
+      <c r="M36">
+        <v>0.5335785920000001</v>
+      </c>
+      <c r="N36">
+        <v>2.255421408</v>
+      </c>
+      <c r="O36">
+        <v>0.3383132112</v>
+      </c>
+      <c r="P36">
+        <v>1.9171081968</v>
+      </c>
+      <c r="Q36">
+        <v>2.3781081968</v>
+      </c>
+      <c r="R36">
+        <v>0.5151515151515152</v>
+      </c>
+      <c r="S36">
+        <v>0.2922970153981744</v>
+      </c>
+      <c r="T36">
+        <v>1.426790082170757</v>
+      </c>
+      <c r="U36">
+        <v>0.0509</v>
+      </c>
+      <c r="V36">
+        <v>0.15</v>
+      </c>
+      <c r="W36">
+        <v>0.043265</v>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y36">
+        <v>5.2269713249665</v>
+      </c>
+      <c r="Z36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>0.35</v>
+      </c>
+      <c r="B37">
+        <v>0.2074063312215473</v>
+      </c>
+      <c r="C37">
+        <v>21.34426509985735</v>
+      </c>
+      <c r="D37">
+        <v>27.53546509985735</v>
+      </c>
+      <c r="E37">
+        <v>10.4592</v>
+      </c>
+      <c r="F37">
+        <v>10.7912</v>
+      </c>
+      <c r="G37">
+        <v>4.6</v>
+      </c>
+      <c r="H37">
+        <v>30.5</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>3.25</v>
+      </c>
+      <c r="K37">
+        <v>0.461</v>
+      </c>
+      <c r="L37">
+        <v>2.789</v>
+      </c>
+      <c r="M37">
+        <v>0.5492720800000001</v>
+      </c>
+      <c r="N37">
+        <v>2.23972792</v>
+      </c>
+      <c r="O37">
+        <v>0.335959188</v>
+      </c>
+      <c r="P37">
+        <v>1.903768732</v>
+      </c>
+      <c r="Q37">
+        <v>2.364768732</v>
+      </c>
+      <c r="R37">
+        <v>0.5384615384615385</v>
+      </c>
+      <c r="S37">
+        <v>0.2957901249562266</v>
+      </c>
+      <c r="T37">
+        <v>1.446450803089054</v>
+      </c>
+      <c r="U37">
+        <v>0.0509</v>
+      </c>
+      <c r="V37">
+        <v>0.15</v>
+      </c>
+      <c r="W37">
+        <v>0.043265</v>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y37">
+        <v>5.077629287110315</v>
+      </c>
+      <c r="Z37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>0.36</v>
+      </c>
+      <c r="B38">
+        <v>0.2071865322802994</v>
+      </c>
+      <c r="C38">
+        <v>21.07188779666187</v>
+      </c>
+      <c r="D38">
+        <v>27.57140779666187</v>
+      </c>
+      <c r="E38">
+        <v>10.76752</v>
+      </c>
+      <c r="F38">
+        <v>11.09952</v>
+      </c>
+      <c r="G38">
+        <v>4.6</v>
+      </c>
+      <c r="H38">
+        <v>30.5</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>3.25</v>
+      </c>
+      <c r="K38">
+        <v>0.461</v>
+      </c>
+      <c r="L38">
+        <v>2.789</v>
+      </c>
+      <c r="M38">
+        <v>0.564965568</v>
+      </c>
+      <c r="N38">
+        <v>2.224034432</v>
+      </c>
+      <c r="O38">
+        <v>0.3336051648</v>
+      </c>
+      <c r="P38">
+        <v>1.8904292672</v>
+      </c>
+      <c r="Q38">
+        <v>2.3514292672</v>
+      </c>
+      <c r="R38">
+        <v>0.5625</v>
+      </c>
+      <c r="S38">
+        <v>0.2993923941879679</v>
+      </c>
+      <c r="T38">
+        <v>1.466725921536048</v>
+      </c>
+      <c r="U38">
+        <v>0.0509</v>
+      </c>
+      <c r="V38">
+        <v>0.15</v>
+      </c>
+      <c r="W38">
+        <v>0.043265</v>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y38">
+        <v>4.936584029135029</v>
+      </c>
+      <c r="Z38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>0.37</v>
+      </c>
+      <c r="B39">
+        <v>0.2069667333390516</v>
+      </c>
+      <c r="C39">
+        <v>20.79960444982204</v>
+      </c>
+      <c r="D39">
+        <v>27.60744444982204</v>
+      </c>
+      <c r="E39">
+        <v>11.07584</v>
+      </c>
+      <c r="F39">
+        <v>11.40784</v>
+      </c>
+      <c r="G39">
+        <v>4.6</v>
+      </c>
+      <c r="H39">
+        <v>30.5</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>3.25</v>
+      </c>
+      <c r="K39">
+        <v>0.461</v>
+      </c>
+      <c r="L39">
+        <v>2.789</v>
+      </c>
+      <c r="M39">
+        <v>0.580659056</v>
+      </c>
+      <c r="N39">
+        <v>2.208340944</v>
+      </c>
+      <c r="O39">
+        <v>0.3312511416</v>
+      </c>
+      <c r="P39">
+        <v>1.8770898024</v>
+      </c>
+      <c r="Q39">
+        <v>2.3380898024</v>
+      </c>
+      <c r="R39">
+        <v>0.5873015873015873</v>
+      </c>
+      <c r="S39">
+        <v>0.3031090211730978</v>
+      </c>
+      <c r="T39">
+        <v>1.487644694536914</v>
+      </c>
+      <c r="U39">
+        <v>0.0509</v>
+      </c>
+      <c r="V39">
+        <v>0.15</v>
+      </c>
+      <c r="W39">
+        <v>0.043265</v>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y39">
+        <v>4.803162839158406</v>
+      </c>
+      <c r="Z39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>0.38</v>
+      </c>
+      <c r="B40">
+        <v>0.2067469343978038</v>
+      </c>
+      <c r="C40">
+        <v>20.52741542823129</v>
+      </c>
+      <c r="D40">
+        <v>27.6435754282313</v>
+      </c>
+      <c r="E40">
+        <v>11.38416</v>
+      </c>
+      <c r="F40">
+        <v>11.71616</v>
+      </c>
+      <c r="G40">
+        <v>4.6</v>
+      </c>
+      <c r="H40">
+        <v>30.5</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>3.25</v>
+      </c>
+      <c r="K40">
+        <v>0.461</v>
+      </c>
+      <c r="L40">
+        <v>2.789</v>
+      </c>
+      <c r="M40">
+        <v>0.596352544</v>
+      </c>
+      <c r="N40">
+        <v>2.192647456</v>
+      </c>
+      <c r="O40">
+        <v>0.3288971184</v>
+      </c>
+      <c r="P40">
+        <v>1.8637503376</v>
+      </c>
+      <c r="Q40">
+        <v>2.3247503376</v>
+      </c>
+      <c r="R40">
+        <v>0.6129032258064516</v>
+      </c>
+      <c r="S40">
+        <v>0.3069455393512964</v>
+      </c>
+      <c r="T40">
+        <v>1.509238266666841</v>
+      </c>
+      <c r="U40">
+        <v>0.0509</v>
+      </c>
+      <c r="V40">
+        <v>0.15</v>
+      </c>
+      <c r="W40">
+        <v>0.043265</v>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y40">
+        <v>4.67676381707529</v>
+      </c>
+      <c r="Z40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>0.39</v>
+      </c>
+      <c r="B41">
+        <v>0.206527135456556</v>
+      </c>
+      <c r="C41">
+        <v>20.25532110271677</v>
+      </c>
+      <c r="D41">
+        <v>27.67980110271677</v>
+      </c>
+      <c r="E41">
+        <v>11.69248</v>
+      </c>
+      <c r="F41">
+        <v>12.02448</v>
+      </c>
+      <c r="G41">
+        <v>4.6</v>
+      </c>
+      <c r="H41">
+        <v>30.5</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>3.25</v>
+      </c>
+      <c r="K41">
+        <v>0.461</v>
+      </c>
+      <c r="L41">
+        <v>2.789</v>
+      </c>
+      <c r="M41">
+        <v>0.6120460320000001</v>
+      </c>
+      <c r="N41">
+        <v>2.176953968</v>
+      </c>
+      <c r="O41">
+        <v>0.3265430952</v>
+      </c>
+      <c r="P41">
+        <v>1.8504108728</v>
+      </c>
+      <c r="Q41">
+        <v>2.3114108728</v>
+      </c>
+      <c r="R41">
+        <v>0.639344262295082</v>
+      </c>
+      <c r="S41">
+        <v>0.3109078450107475</v>
+      </c>
+      <c r="T41">
+        <v>1.53153982476824</v>
+      </c>
+      <c r="U41">
+        <v>0.0509</v>
+      </c>
+      <c r="V41">
+        <v>0.15</v>
+      </c>
+      <c r="W41">
+        <v>0.043265</v>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y41">
+        <v>4.556846796124642</v>
+      </c>
+      <c r="Z41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>0.4</v>
+      </c>
+      <c r="B42">
+        <v>0.2071913365153081</v>
+      </c>
+      <c r="C42">
+        <v>19.83782117945627</v>
+      </c>
+      <c r="D42">
+        <v>27.57062117945627</v>
+      </c>
+      <c r="E42">
+        <v>12.0008</v>
+      </c>
+      <c r="F42">
+        <v>12.3328</v>
+      </c>
+      <c r="G42">
+        <v>4.6</v>
+      </c>
+      <c r="H42">
+        <v>30.5</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>3.25</v>
+      </c>
+      <c r="K42">
+        <v>0.461</v>
+      </c>
+      <c r="L42">
+        <v>2.789</v>
+      </c>
+      <c r="M42">
+        <v>0.6598048</v>
+      </c>
+      <c r="N42">
+        <v>2.1291952</v>
+      </c>
+      <c r="O42">
+        <v>0.31937928</v>
+      </c>
+      <c r="P42">
+        <v>1.80981592</v>
+      </c>
+      <c r="Q42">
+        <v>2.27081592</v>
+      </c>
+      <c r="R42">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="S42">
+        <v>0.3150022275255135</v>
+      </c>
+      <c r="T42">
+        <v>1.554584768139687</v>
+      </c>
+      <c r="U42">
+        <v>0.0535</v>
+      </c>
+      <c r="V42">
+        <v>0.15</v>
+      </c>
+      <c r="W42">
+        <v>0.04547499999999999</v>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y42">
+        <v>4.227007745321041</v>
+      </c>
+      <c r="Z42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>0.41</v>
+      </c>
+      <c r="B43">
+        <v>0.2069936375740603</v>
+      </c>
+      <c r="C43">
+        <v>19.56190836616882</v>
+      </c>
+      <c r="D43">
+        <v>27.60302836616882</v>
+      </c>
+      <c r="E43">
+        <v>12.30912</v>
+      </c>
+      <c r="F43">
+        <v>12.64112</v>
+      </c>
+      <c r="G43">
+        <v>4.6</v>
+      </c>
+      <c r="H43">
+        <v>30.5</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>3.25</v>
+      </c>
+      <c r="K43">
+        <v>0.461</v>
+      </c>
+      <c r="L43">
+        <v>2.789</v>
+      </c>
+      <c r="M43">
+        <v>0.6762999200000001</v>
+      </c>
+      <c r="N43">
+        <v>2.11270008</v>
+      </c>
+      <c r="O43">
+        <v>0.316905012</v>
+      </c>
+      <c r="P43">
+        <v>1.795795068</v>
+      </c>
+      <c r="Q43">
+        <v>2.256795068</v>
+      </c>
+      <c r="R43">
+        <v>0.6949152542372882</v>
+      </c>
+      <c r="S43">
+        <v>0.3192354026678988</v>
+      </c>
+      <c r="T43">
+        <v>1.578410896032199</v>
+      </c>
+      <c r="U43">
+        <v>0.0535</v>
+      </c>
+      <c r="V43">
+        <v>0.15</v>
+      </c>
+      <c r="W43">
+        <v>0.04547499999999999</v>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y43">
+        <v>4.123909995435161</v>
+      </c>
+      <c r="Z43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>0.42</v>
+      </c>
+      <c r="B44">
+        <v>0.2067959386328125</v>
+      </c>
+      <c r="C44">
+        <v>19.28607182694552</v>
+      </c>
+      <c r="D44">
+        <v>27.63551182694552</v>
+      </c>
+      <c r="E44">
+        <v>12.61744</v>
+      </c>
+      <c r="F44">
+        <v>12.94944</v>
+      </c>
+      <c r="G44">
+        <v>4.6</v>
+      </c>
+      <c r="H44">
+        <v>30.5</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>3.25</v>
+      </c>
+      <c r="K44">
+        <v>0.461</v>
+      </c>
+      <c r="L44">
+        <v>2.789</v>
+      </c>
+      <c r="M44">
+        <v>0.6927950399999999</v>
+      </c>
+      <c r="N44">
+        <v>2.09620496</v>
+      </c>
+      <c r="O44">
+        <v>0.314430744</v>
+      </c>
+      <c r="P44">
+        <v>1.781774216</v>
+      </c>
+      <c r="Q44">
+        <v>2.242774216</v>
+      </c>
+      <c r="R44">
+        <v>0.7241379310344827</v>
+      </c>
+      <c r="S44">
+        <v>0.323614549366918</v>
+      </c>
+      <c r="T44">
+        <v>1.603058614541695</v>
+      </c>
+      <c r="U44">
+        <v>0.0535</v>
+      </c>
+      <c r="V44">
+        <v>0.15</v>
+      </c>
+      <c r="W44">
+        <v>0.04547499999999999</v>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y44">
+        <v>4.025721662210515</v>
+      </c>
+      <c r="Z44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>0.43</v>
+      </c>
+      <c r="B45">
+        <v>0.2075850896915646</v>
+      </c>
+      <c r="C45">
+        <v>18.84854258543464</v>
+      </c>
+      <c r="D45">
+        <v>27.50630258543464</v>
+      </c>
+      <c r="E45">
+        <v>12.92576</v>
+      </c>
+      <c r="F45">
+        <v>13.25776</v>
+      </c>
+      <c r="G45">
+        <v>4.6</v>
+      </c>
+      <c r="H45">
+        <v>30.5</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>3.25</v>
+      </c>
+      <c r="K45">
+        <v>0.461</v>
+      </c>
+      <c r="L45">
+        <v>2.789</v>
+      </c>
+      <c r="M45">
+        <v>0.745086112</v>
+      </c>
+      <c r="N45">
+        <v>2.043913888</v>
+      </c>
+      <c r="O45">
+        <v>0.3065870832</v>
+      </c>
+      <c r="P45">
+        <v>1.7373268048</v>
+      </c>
+      <c r="Q45">
+        <v>2.1983268048</v>
+      </c>
+      <c r="R45">
+        <v>0.7543859649122806</v>
+      </c>
+      <c r="S45">
+        <v>0.3281473503360783</v>
+      </c>
+      <c r="T45">
+        <v>1.628571165279593</v>
+      </c>
+      <c r="U45">
+        <v>0.0562</v>
+      </c>
+      <c r="V45">
+        <v>0.15</v>
+      </c>
+      <c r="W45">
+        <v>0.04777</v>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y45">
+        <v>3.743191498380794</v>
+      </c>
+      <c r="Z45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>0.44</v>
+      </c>
+      <c r="B46">
+        <v>0.2074103407503168</v>
+      </c>
+      <c r="C46">
+        <v>18.56873031060179</v>
+      </c>
+      <c r="D46">
+        <v>27.53481031060178</v>
+      </c>
+      <c r="E46">
+        <v>13.23408</v>
+      </c>
+      <c r="F46">
+        <v>13.56608</v>
+      </c>
+      <c r="G46">
+        <v>4.6</v>
+      </c>
+      <c r="H46">
+        <v>30.5</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>3.25</v>
+      </c>
+      <c r="K46">
+        <v>0.461</v>
+      </c>
+      <c r="L46">
+        <v>2.789</v>
+      </c>
+      <c r="M46">
+        <v>0.7624136960000001</v>
+      </c>
+      <c r="N46">
+        <v>2.026586304</v>
+      </c>
+      <c r="O46">
+        <v>0.3039879456</v>
+      </c>
+      <c r="P46">
+        <v>1.7225983584</v>
+      </c>
+      <c r="Q46">
+        <v>2.1835983584</v>
+      </c>
+      <c r="R46">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="S46">
+        <v>0.3328420370541371</v>
+      </c>
+      <c r="T46">
+        <v>1.654994878543846</v>
+      </c>
+      <c r="U46">
+        <v>0.0562</v>
+      </c>
+      <c r="V46">
+        <v>0.15</v>
+      </c>
+      <c r="W46">
+        <v>0.04777</v>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y46">
+        <v>3.658118964326685</v>
+      </c>
+      <c r="Z46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>0.45</v>
+      </c>
+      <c r="B47">
+        <v>0.2072355918090689</v>
+      </c>
+      <c r="C47">
+        <v>18.28897718828813</v>
+      </c>
+      <c r="D47">
+        <v>27.56337718828813</v>
+      </c>
+      <c r="E47">
+        <v>13.5424</v>
+      </c>
+      <c r="F47">
+        <v>13.8744</v>
+      </c>
+      <c r="G47">
+        <v>4.6</v>
+      </c>
+      <c r="H47">
+        <v>30.5</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>3.25</v>
+      </c>
+      <c r="K47">
+        <v>0.461</v>
+      </c>
+      <c r="L47">
+        <v>2.789</v>
+      </c>
+      <c r="M47">
+        <v>0.7797412800000001</v>
+      </c>
+      <c r="N47">
+        <v>2.00925872</v>
+      </c>
+      <c r="O47">
+        <v>0.301388808</v>
+      </c>
+      <c r="P47">
+        <v>1.707869912</v>
+      </c>
+      <c r="Q47">
+        <v>2.168869912</v>
+      </c>
+      <c r="R47">
+        <v>0.8181818181818181</v>
+      </c>
+      <c r="S47">
+        <v>0.3377074396528526</v>
+      </c>
+      <c r="T47">
+        <v>1.682379454108616</v>
+      </c>
+      <c r="U47">
+        <v>0.0562</v>
+      </c>
+      <c r="V47">
+        <v>0.15</v>
+      </c>
+      <c r="W47">
+        <v>0.04777</v>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y47">
+        <v>3.576827431786092</v>
+      </c>
+      <c r="Z47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>0.46</v>
+      </c>
+      <c r="B48">
+        <v>0.2088985428678211</v>
+      </c>
+      <c r="C48">
+        <v>17.71118664194919</v>
+      </c>
+      <c r="D48">
+        <v>27.2939066419492</v>
+      </c>
+      <c r="E48">
+        <v>13.85072</v>
+      </c>
+      <c r="F48">
+        <v>14.18272</v>
+      </c>
+      <c r="G48">
+        <v>4.6</v>
+      </c>
+      <c r="H48">
+        <v>30.5</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>3.25</v>
+      </c>
+      <c r="K48">
+        <v>0.461</v>
+      </c>
+      <c r="L48">
+        <v>2.789</v>
+      </c>
+      <c r="M48">
+        <v>0.8637276480000001</v>
+      </c>
+      <c r="N48">
+        <v>1.925272352</v>
+      </c>
+      <c r="O48">
+        <v>0.2887908528</v>
+      </c>
+      <c r="P48">
+        <v>1.6364814992</v>
+      </c>
+      <c r="Q48">
+        <v>2.0974814992</v>
+      </c>
+      <c r="R48">
+        <v>0.8518518518518519</v>
+      </c>
+      <c r="S48">
+        <v>0.3427530423478169</v>
+      </c>
+      <c r="T48">
+        <v>1.710778273212823</v>
+      </c>
+      <c r="U48">
+        <v>0.0609</v>
+      </c>
+      <c r="V48">
+        <v>0.15</v>
+      </c>
+      <c r="W48">
+        <v>0.051765</v>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y48">
+        <v>3.229027120363756</v>
+      </c>
+      <c r="Z48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>0.47</v>
+      </c>
+      <c r="B49">
+        <v>0.2087637439265733</v>
+      </c>
+      <c r="C49">
+        <v>17.42451355106553</v>
+      </c>
+      <c r="D49">
+        <v>27.31555355106553</v>
+      </c>
+      <c r="E49">
+        <v>14.15904</v>
+      </c>
+      <c r="F49">
+        <v>14.49104</v>
+      </c>
+      <c r="G49">
+        <v>4.6</v>
+      </c>
+      <c r="H49">
+        <v>30.5</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>3.25</v>
+      </c>
+      <c r="K49">
+        <v>0.461</v>
+      </c>
+      <c r="L49">
+        <v>2.789</v>
+      </c>
+      <c r="M49">
+        <v>0.8825043360000001</v>
+      </c>
+      <c r="N49">
+        <v>1.906495664</v>
+      </c>
+      <c r="O49">
+        <v>0.2859743496</v>
+      </c>
+      <c r="P49">
+        <v>1.6205213144</v>
+      </c>
+      <c r="Q49">
+        <v>2.0815213144</v>
+      </c>
+      <c r="R49">
+        <v>0.8867924528301887</v>
+      </c>
+      <c r="S49">
+        <v>0.3479890451444779</v>
+      </c>
+      <c r="T49">
+        <v>1.740248745868132</v>
+      </c>
+      <c r="U49">
+        <v>0.0609</v>
+      </c>
+      <c r="V49">
+        <v>0.15</v>
+      </c>
+      <c r="W49">
+        <v>0.051765</v>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y49">
+        <v>3.160324415675165</v>
+      </c>
+      <c r="Z49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>0.48</v>
+      </c>
+      <c r="B50">
+        <v>0.2086289449853255</v>
+      </c>
+      <c r="C50">
+        <v>17.13787482394043</v>
+      </c>
+      <c r="D50">
+        <v>27.33723482394043</v>
+      </c>
+      <c r="E50">
+        <v>14.46736</v>
+      </c>
+      <c r="F50">
+        <v>14.79936</v>
+      </c>
+      <c r="G50">
+        <v>4.6</v>
+      </c>
+      <c r="H50">
+        <v>30.5</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>3.25</v>
+      </c>
+      <c r="K50">
+        <v>0.461</v>
+      </c>
+      <c r="L50">
+        <v>2.789</v>
+      </c>
+      <c r="M50">
+        <v>0.9012810240000001</v>
+      </c>
+      <c r="N50">
+        <v>1.887718976</v>
+      </c>
+      <c r="O50">
+        <v>0.2831578464</v>
+      </c>
+      <c r="P50">
+        <v>1.6045611296</v>
+      </c>
+      <c r="Q50">
+        <v>2.0655611296</v>
+      </c>
+      <c r="R50">
+        <v>0.923076923076923</v>
+      </c>
+      <c r="S50">
+        <v>0.3534264326640874</v>
+      </c>
+      <c r="T50">
+        <v>1.770852698240952</v>
+      </c>
+      <c r="U50">
+        <v>0.0609</v>
+      </c>
+      <c r="V50">
+        <v>0.15</v>
+      </c>
+      <c r="W50">
+        <v>0.051765</v>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y50">
+        <v>3.094484323681933</v>
+      </c>
+      <c r="Z50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>0.49</v>
+      </c>
+      <c r="B51">
+        <v>0.2084941460440776</v>
+      </c>
+      <c r="C51">
+        <v>16.85127054246588</v>
+      </c>
+      <c r="D51">
+        <v>27.35895054246589</v>
+      </c>
+      <c r="E51">
+        <v>14.77568</v>
+      </c>
+      <c r="F51">
+        <v>15.10768</v>
+      </c>
+      <c r="G51">
+        <v>4.6</v>
+      </c>
+      <c r="H51">
+        <v>30.5</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>3.25</v>
+      </c>
+      <c r="K51">
+        <v>0.461</v>
+      </c>
+      <c r="L51">
+        <v>2.789</v>
+      </c>
+      <c r="M51">
+        <v>0.9200577120000001</v>
+      </c>
+      <c r="N51">
+        <v>1.868942288</v>
+      </c>
+      <c r="O51">
+        <v>0.2803413432</v>
+      </c>
+      <c r="P51">
+        <v>1.5886009448</v>
+      </c>
+      <c r="Q51">
+        <v>2.0496009448</v>
+      </c>
+      <c r="R51">
+        <v>0.9607843137254901</v>
+      </c>
+      <c r="S51">
+        <v>0.3590770510668189</v>
+      </c>
+      <c r="T51">
+        <v>1.802656805608785</v>
+      </c>
+      <c r="U51">
+        <v>0.0609</v>
+      </c>
+      <c r="V51">
+        <v>0.15</v>
+      </c>
+      <c r="W51">
+        <v>0.051765</v>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y51">
+        <v>3.031331582382301</v>
+      </c>
+      <c r="Z51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>0.5</v>
+      </c>
+      <c r="B52">
+        <v>0.2123118471028298</v>
+      </c>
+      <c r="C52">
+        <v>15.94098418572242</v>
+      </c>
+      <c r="D52">
+        <v>26.75698418572242</v>
+      </c>
+      <c r="E52">
+        <v>15.084</v>
+      </c>
+      <c r="F52">
+        <v>15.416</v>
+      </c>
+      <c r="G52">
+        <v>4.6</v>
+      </c>
+      <c r="H52">
+        <v>30.5</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>3.25</v>
+      </c>
+      <c r="K52">
+        <v>0.461</v>
+      </c>
+      <c r="L52">
+        <v>2.789</v>
+      </c>
+      <c r="M52">
+        <v>1.0822032</v>
+      </c>
+      <c r="N52">
+        <v>1.7067968</v>
+      </c>
+      <c r="O52">
+        <v>0.25601952</v>
+      </c>
+      <c r="P52">
+        <v>1.45077728</v>
+      </c>
+      <c r="Q52">
+        <v>1.91177728</v>
+      </c>
+      <c r="R52">
+        <v>1</v>
+      </c>
+      <c r="S52">
+        <v>0.3649536942056596</v>
+      </c>
+      <c r="T52">
+        <v>1.835733077271332</v>
+      </c>
+      <c r="U52">
+        <v>0.0702</v>
+      </c>
+      <c r="V52">
+        <v>0.15</v>
+      </c>
+      <c r="W52">
+        <v>0.05966999999999999</v>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>B1/B+</t>
+        </is>
+      </c>
+      <c r="Y52">
+        <v>2.577150021363825</v>
+      </c>
+      <c r="Z52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>0.51</v>
+      </c>
+      <c r="B53">
+        <v>0.212256098161582</v>
+      </c>
+      <c r="C53">
+        <v>15.64126390377874</v>
+      </c>
+      <c r="D53">
+        <v>26.76558390377874</v>
+      </c>
+      <c r="E53">
+        <v>15.39232</v>
+      </c>
+      <c r="F53">
+        <v>15.72432</v>
+      </c>
+      <c r="G53">
+        <v>4.6</v>
+      </c>
+      <c r="H53">
+        <v>30.5</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>3.25</v>
+      </c>
+      <c r="K53">
+        <v>0.461</v>
+      </c>
+      <c r="L53">
+        <v>2.789</v>
+      </c>
+      <c r="M53">
+        <v>1.103847264</v>
+      </c>
+      <c r="N53">
+        <v>1.685152736</v>
+      </c>
+      <c r="O53">
+        <v>0.2527729104</v>
+      </c>
+      <c r="P53">
+        <v>1.4323798256</v>
+      </c>
+      <c r="Q53">
+        <v>1.8933798256</v>
+      </c>
+      <c r="R53">
+        <v>1.040816326530612</v>
+      </c>
+      <c r="S53">
+        <v>0.3710702003297591</v>
+      </c>
+      <c r="T53">
+        <v>1.870159400838473</v>
+      </c>
+      <c r="U53">
+        <v>0.0702</v>
+      </c>
+      <c r="V53">
+        <v>0.15</v>
+      </c>
+      <c r="W53">
+        <v>0.05966999999999999</v>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>B1/B+</t>
+        </is>
+      </c>
+      <c r="Y53">
+        <v>2.52661766800375</v>
+      </c>
+      <c r="Z53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>0.52</v>
+      </c>
+      <c r="B54">
+        <v>0.2142777492203341</v>
+      </c>
+      <c r="C54">
+        <v>15.02458189618739</v>
+      </c>
+      <c r="D54">
+        <v>26.45722189618738</v>
+      </c>
+      <c r="E54">
+        <v>15.70064</v>
+      </c>
+      <c r="F54">
+        <v>16.03264</v>
+      </c>
+      <c r="G54">
+        <v>4.6</v>
+      </c>
+      <c r="H54">
+        <v>30.5</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>3.25</v>
+      </c>
+      <c r="K54">
+        <v>0.461</v>
+      </c>
+      <c r="L54">
+        <v>2.789</v>
+      </c>
+      <c r="M54">
+        <v>1.200844736</v>
+      </c>
+      <c r="N54">
+        <v>1.588155264</v>
+      </c>
+      <c r="O54">
+        <v>0.2382232896</v>
+      </c>
+      <c r="P54">
+        <v>1.3499319744</v>
+      </c>
+      <c r="Q54">
+        <v>1.8109319744</v>
+      </c>
+      <c r="R54">
+        <v>1.083333333333333</v>
+      </c>
+      <c r="S54">
+        <v>0.3774415608756961</v>
+      </c>
+      <c r="T54">
+        <v>1.906020154554244</v>
+      </c>
+      <c r="U54">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V54">
+        <v>0.15</v>
+      </c>
+      <c r="W54">
+        <v>0.063665</v>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y54">
+        <v>2.322531728198374</v>
+      </c>
+      <c r="Z54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>0.53</v>
+      </c>
+      <c r="B55">
+        <v>0.2142619502790863</v>
+      </c>
+      <c r="C55">
+        <v>14.71864415680659</v>
+      </c>
+      <c r="D55">
+        <v>26.45960415680659</v>
+      </c>
+      <c r="E55">
+        <v>16.00896</v>
+      </c>
+      <c r="F55">
+        <v>16.34096</v>
+      </c>
+      <c r="G55">
+        <v>4.6</v>
+      </c>
+      <c r="H55">
+        <v>30.5</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>3.25</v>
+      </c>
+      <c r="K55">
+        <v>0.461</v>
+      </c>
+      <c r="L55">
+        <v>2.789</v>
+      </c>
+      <c r="M55">
+        <v>1.223937904</v>
+      </c>
+      <c r="N55">
+        <v>1.565062096</v>
+      </c>
+      <c r="O55">
+        <v>0.2347593144</v>
+      </c>
+      <c r="P55">
+        <v>1.3303027816</v>
+      </c>
+      <c r="Q55">
+        <v>1.7913027816</v>
+      </c>
+      <c r="R55">
+        <v>1.127659574468085</v>
+      </c>
+      <c r="S55">
+        <v>0.3840840431469921</v>
+      </c>
+      <c r="T55">
+        <v>1.943406897789835</v>
+      </c>
+      <c r="U55">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V55">
+        <v>0.15</v>
+      </c>
+      <c r="W55">
+        <v>0.063665</v>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y55">
+        <v>2.27871037483614</v>
+      </c>
+      <c r="Z55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>0.54</v>
+      </c>
+      <c r="B56">
+        <v>0.2142461513378385</v>
+      </c>
+      <c r="C56">
+        <v>14.41270684647134</v>
+      </c>
+      <c r="D56">
+        <v>26.46198684647134</v>
+      </c>
+      <c r="E56">
+        <v>16.31728</v>
+      </c>
+      <c r="F56">
+        <v>16.64928</v>
+      </c>
+      <c r="G56">
+        <v>4.6</v>
+      </c>
+      <c r="H56">
+        <v>30.5</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>3.25</v>
+      </c>
+      <c r="K56">
+        <v>0.461</v>
+      </c>
+      <c r="L56">
+        <v>2.789</v>
+      </c>
+      <c r="M56">
+        <v>1.247031072</v>
+      </c>
+      <c r="N56">
+        <v>1.541968928</v>
+      </c>
+      <c r="O56">
+        <v>0.2312953392</v>
+      </c>
+      <c r="P56">
+        <v>1.3106735888</v>
+      </c>
+      <c r="Q56">
+        <v>1.7716735888</v>
+      </c>
+      <c r="R56">
+        <v>1.173913043478261</v>
+      </c>
+      <c r="S56">
+        <v>0.3910153289953011</v>
+      </c>
+      <c r="T56">
+        <v>1.982419151600886</v>
+      </c>
+      <c r="U56">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V56">
+        <v>0.15</v>
+      </c>
+      <c r="W56">
+        <v>0.063665</v>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y56">
+        <v>2.236512034561397</v>
+      </c>
+      <c r="Z56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>0.55</v>
+      </c>
+      <c r="B57">
+        <v>0.2142303523965907</v>
+      </c>
+      <c r="C57">
+        <v>14.10676996529757</v>
+      </c>
+      <c r="D57">
+        <v>26.46436996529757</v>
+      </c>
+      <c r="E57">
+        <v>16.6256</v>
+      </c>
+      <c r="F57">
+        <v>16.9576</v>
+      </c>
+      <c r="G57">
+        <v>4.6</v>
+      </c>
+      <c r="H57">
+        <v>30.5</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>3.25</v>
+      </c>
+      <c r="K57">
+        <v>0.461</v>
+      </c>
+      <c r="L57">
+        <v>2.789</v>
+      </c>
+      <c r="M57">
+        <v>1.27012424</v>
+      </c>
+      <c r="N57">
+        <v>1.51887576</v>
+      </c>
+      <c r="O57">
+        <v>0.227831364</v>
+      </c>
+      <c r="P57">
+        <v>1.291044396</v>
+      </c>
+      <c r="Q57">
+        <v>1.752044396</v>
+      </c>
+      <c r="R57">
+        <v>1.222222222222223</v>
+      </c>
+      <c r="S57">
+        <v>0.3982546719924237</v>
+      </c>
+      <c r="T57">
+        <v>2.023165283359096</v>
+      </c>
+      <c r="U57">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V57">
+        <v>0.15</v>
+      </c>
+      <c r="W57">
+        <v>0.063665</v>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y57">
+        <v>2.195848179387554</v>
+      </c>
+      <c r="Z57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="B58">
+        <v>0.2142145534553428</v>
+      </c>
+      <c r="C58">
+        <v>13.80083351340124</v>
+      </c>
+      <c r="D58">
+        <v>26.46675351340124</v>
+      </c>
+      <c r="E58">
+        <v>16.93392</v>
+      </c>
+      <c r="F58">
+        <v>17.26592</v>
+      </c>
+      <c r="G58">
+        <v>4.6</v>
+      </c>
+      <c r="H58">
+        <v>30.5</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>3.25</v>
+      </c>
+      <c r="K58">
+        <v>0.461</v>
+      </c>
+      <c r="L58">
+        <v>2.789</v>
+      </c>
+      <c r="M58">
+        <v>1.293217408</v>
+      </c>
+      <c r="N58">
+        <v>1.495782592</v>
+      </c>
+      <c r="O58">
+        <v>0.2243673888</v>
+      </c>
+      <c r="P58">
+        <v>1.2714152032</v>
+      </c>
+      <c r="Q58">
+        <v>1.7324152032</v>
+      </c>
+      <c r="R58">
+        <v>1.272727272727273</v>
+      </c>
+      <c r="S58">
+        <v>0.4058230760348701</v>
+      </c>
+      <c r="T58">
+        <v>2.065763512015406</v>
+      </c>
+      <c r="U58">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V58">
+        <v>0.15</v>
+      </c>
+      <c r="W58">
+        <v>0.063665</v>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y58">
+        <v>2.156636604755633</v>
+      </c>
+      <c r="Z58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>0.5700000000000001</v>
+      </c>
+      <c r="B59">
+        <v>0.214198754514095</v>
+      </c>
+      <c r="C59">
+        <v>13.49489749089832</v>
+      </c>
+      <c r="D59">
+        <v>26.46913749089832</v>
+      </c>
+      <c r="E59">
+        <v>17.24224</v>
+      </c>
+      <c r="F59">
+        <v>17.57424</v>
+      </c>
+      <c r="G59">
+        <v>4.6</v>
+      </c>
+      <c r="H59">
+        <v>30.5</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>3.25</v>
+      </c>
+      <c r="K59">
+        <v>0.461</v>
+      </c>
+      <c r="L59">
+        <v>2.789</v>
+      </c>
+      <c r="M59">
+        <v>1.316310576</v>
+      </c>
+      <c r="N59">
+        <v>1.472689424</v>
+      </c>
+      <c r="O59">
+        <v>0.2209034136</v>
+      </c>
+      <c r="P59">
+        <v>1.2517860104</v>
+      </c>
+      <c r="Q59">
+        <v>1.7127860104</v>
+      </c>
+      <c r="R59">
+        <v>1.325581395348838</v>
+      </c>
+      <c r="S59">
+        <v>0.4137434988699884</v>
+      </c>
+      <c r="T59">
+        <v>2.110343053632475</v>
+      </c>
+      <c r="U59">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V59">
+        <v>0.15</v>
+      </c>
+      <c r="W59">
+        <v>0.063665</v>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y59">
+        <v>2.118800874847639</v>
+      </c>
+      <c r="Z59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>0.58</v>
+      </c>
+      <c r="B60">
+        <v>0.2141829555728472</v>
+      </c>
+      <c r="C60">
+        <v>13.18896189790488</v>
+      </c>
+      <c r="D60">
+        <v>26.47152189790488</v>
+      </c>
+      <c r="E60">
+        <v>17.55056</v>
+      </c>
+      <c r="F60">
+        <v>17.88256</v>
+      </c>
+      <c r="G60">
+        <v>4.6</v>
+      </c>
+      <c r="H60">
+        <v>30.5</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>3.25</v>
+      </c>
+      <c r="K60">
+        <v>0.461</v>
+      </c>
+      <c r="L60">
+        <v>2.789</v>
+      </c>
+      <c r="M60">
+        <v>1.339403744</v>
+      </c>
+      <c r="N60">
+        <v>1.449596256</v>
+      </c>
+      <c r="O60">
+        <v>0.2174394384</v>
+      </c>
+      <c r="P60">
+        <v>1.2321568176</v>
+      </c>
+      <c r="Q60">
+        <v>1.6931568176</v>
+      </c>
+      <c r="R60">
+        <v>1.380952380952381</v>
+      </c>
+      <c r="S60">
+        <v>0.4220410846972551</v>
+      </c>
+      <c r="T60">
+        <v>2.157045430564641</v>
+      </c>
+      <c r="U60">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V60">
+        <v>0.15</v>
+      </c>
+      <c r="W60">
+        <v>0.063665</v>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y60">
+        <v>2.082269825281301</v>
+      </c>
+      <c r="Z60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>0.59</v>
+      </c>
+      <c r="B61">
+        <v>0.2141671566315993</v>
+      </c>
+      <c r="C61">
+        <v>12.88302673453701</v>
+      </c>
+      <c r="D61">
+        <v>26.47390673453701</v>
+      </c>
+      <c r="E61">
+        <v>17.85888</v>
+      </c>
+      <c r="F61">
+        <v>18.19088</v>
+      </c>
+      <c r="G61">
+        <v>4.6</v>
+      </c>
+      <c r="H61">
+        <v>30.5</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>3.25</v>
+      </c>
+      <c r="K61">
+        <v>0.461</v>
+      </c>
+      <c r="L61">
+        <v>2.789</v>
+      </c>
+      <c r="M61">
+        <v>1.362496912</v>
+      </c>
+      <c r="N61">
+        <v>1.426503088</v>
+      </c>
+      <c r="O61">
+        <v>0.2139754632</v>
+      </c>
+      <c r="P61">
+        <v>1.2125276248</v>
+      </c>
+      <c r="Q61">
+        <v>1.6735276248</v>
+      </c>
+      <c r="R61">
+        <v>1.439024390243902</v>
+      </c>
+      <c r="S61">
+        <v>0.4307434308087787</v>
+      </c>
+      <c r="T61">
+        <v>2.206025972225206</v>
+      </c>
+      <c r="U61">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V61">
+        <v>0.15</v>
+      </c>
+      <c r="W61">
+        <v>0.063665</v>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y61">
+        <v>2.046977116378228</v>
+      </c>
+      <c r="Z61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>0.6</v>
+      </c>
+      <c r="B62">
+        <v>0.2141513576903514</v>
+      </c>
+      <c r="C62">
+        <v>12.57709200091082</v>
+      </c>
+      <c r="D62">
+        <v>26.47629200091082</v>
+      </c>
+      <c r="E62">
+        <v>18.1672</v>
+      </c>
+      <c r="F62">
+        <v>18.4992</v>
+      </c>
+      <c r="G62">
+        <v>4.6</v>
+      </c>
+      <c r="H62">
+        <v>30.5</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>3.25</v>
+      </c>
+      <c r="K62">
+        <v>0.461</v>
+      </c>
+      <c r="L62">
+        <v>2.789</v>
+      </c>
+      <c r="M62">
+        <v>1.38559008</v>
+      </c>
+      <c r="N62">
+        <v>1.40340992</v>
+      </c>
+      <c r="O62">
+        <v>0.2105114880000001</v>
+      </c>
+      <c r="P62">
+        <v>1.192898432</v>
+      </c>
+      <c r="Q62">
+        <v>1.653898432</v>
+      </c>
+      <c r="R62">
+        <v>1.5</v>
+      </c>
+      <c r="S62">
+        <v>0.4398808942258786</v>
+      </c>
+      <c r="T62">
+        <v>2.2574555409688</v>
+      </c>
+      <c r="U62">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V62">
+        <v>0.15</v>
+      </c>
+      <c r="W62">
+        <v>0.063665</v>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y62">
+        <v>2.012860831105257</v>
+      </c>
+      <c r="Z62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>0.61</v>
+      </c>
+      <c r="B63">
+        <v>0.2225871087491036</v>
+      </c>
+      <c r="C63">
+        <v>11.05352132419759</v>
+      </c>
+      <c r="D63">
+        <v>25.26104132419759</v>
+      </c>
+      <c r="E63">
+        <v>18.47552</v>
+      </c>
+      <c r="F63">
+        <v>18.80752</v>
+      </c>
+      <c r="G63">
+        <v>4.6</v>
+      </c>
+      <c r="H63">
+        <v>30.5</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>3.25</v>
+      </c>
+      <c r="K63">
+        <v>0.461</v>
+      </c>
+      <c r="L63">
+        <v>2.789</v>
+      </c>
+      <c r="M63">
+        <v>1.715245824</v>
+      </c>
+      <c r="N63">
+        <v>1.073754176</v>
+      </c>
+      <c r="O63">
+        <v>0.1610631264</v>
+      </c>
+      <c r="P63">
+        <v>0.9126910496</v>
+      </c>
+      <c r="Q63">
+        <v>1.3736910496</v>
+      </c>
+      <c r="R63">
+        <v>1.564102564102564</v>
+      </c>
+      <c r="S63">
+        <v>0.4494869455105221</v>
+      </c>
+      <c r="T63">
+        <v>2.311522523494117</v>
+      </c>
+      <c r="U63">
+        <v>0.0912</v>
+      </c>
+      <c r="V63">
+        <v>0.15</v>
+      </c>
+      <c r="W63">
+        <v>0.07752000000000001</v>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y63">
+        <v>1.626005999242707</v>
+      </c>
+      <c r="Z63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>0.62</v>
+      </c>
+      <c r="B64">
+        <v>0.2227098598078558</v>
+      </c>
+      <c r="C64">
+        <v>10.72834078408861</v>
+      </c>
+      <c r="D64">
+        <v>25.24418078408861</v>
+      </c>
+      <c r="E64">
+        <v>18.78384</v>
+      </c>
+      <c r="F64">
+        <v>19.11584</v>
+      </c>
+      <c r="G64">
+        <v>4.6</v>
+      </c>
+      <c r="H64">
+        <v>30.5</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>3.25</v>
+      </c>
+      <c r="K64">
+        <v>0.461</v>
+      </c>
+      <c r="L64">
+        <v>2.789</v>
+      </c>
+      <c r="M64">
+        <v>1.743364608</v>
+      </c>
+      <c r="N64">
+        <v>1.045635392</v>
+      </c>
+      <c r="O64">
+        <v>0.1568453088</v>
+      </c>
+      <c r="P64">
+        <v>0.8887900832000001</v>
+      </c>
+      <c r="Q64">
+        <v>1.3497900832</v>
+      </c>
+      <c r="R64">
+        <v>1.631578947368421</v>
+      </c>
+      <c r="S64">
+        <v>0.4595985784417259</v>
+      </c>
+      <c r="T64">
+        <v>2.368435136678661</v>
+      </c>
+      <c r="U64">
+        <v>0.0912</v>
+      </c>
+      <c r="V64">
+        <v>0.15</v>
+      </c>
+      <c r="W64">
+        <v>0.07752000000000001</v>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y64">
+        <v>1.599780096029115</v>
+      </c>
+      <c r="Z64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>0.63</v>
+      </c>
+      <c r="B65">
+        <v>0.222832610866608</v>
+      </c>
+      <c r="C65">
+        <v>10.40318273617967</v>
+      </c>
+      <c r="D65">
+        <v>25.22734273617967</v>
+      </c>
+      <c r="E65">
+        <v>19.09216</v>
+      </c>
+      <c r="F65">
+        <v>19.42416</v>
+      </c>
+      <c r="G65">
+        <v>4.6</v>
+      </c>
+      <c r="H65">
+        <v>30.5</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>3.25</v>
+      </c>
+      <c r="K65">
+        <v>0.461</v>
+      </c>
+      <c r="L65">
+        <v>2.789</v>
+      </c>
+      <c r="M65">
+        <v>1.771483392</v>
+      </c>
+      <c r="N65">
+        <v>1.017516608</v>
+      </c>
+      <c r="O65">
+        <v>0.1526274912</v>
+      </c>
+      <c r="P65">
+        <v>0.8648891168</v>
+      </c>
+      <c r="Q65">
+        <v>1.3258891168</v>
+      </c>
+      <c r="R65">
+        <v>1.702702702702703</v>
+      </c>
+      <c r="S65">
+        <v>0.4702567861259675</v>
+      </c>
+      <c r="T65">
+        <v>2.428424107332639</v>
+      </c>
+      <c r="U65">
+        <v>0.0912</v>
+      </c>
+      <c r="V65">
+        <v>0.15</v>
+      </c>
+      <c r="W65">
+        <v>0.07752000000000001</v>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y65">
+        <v>1.57438676117151</v>
+      </c>
+      <c r="Z65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>0.64</v>
+      </c>
+      <c r="B66">
+        <v>0.2229553619253602</v>
+      </c>
+      <c r="C66">
+        <v>10.07804713549341</v>
+      </c>
+      <c r="D66">
+        <v>25.21052713549341</v>
+      </c>
+      <c r="E66">
+        <v>19.40048</v>
+      </c>
+      <c r="F66">
+        <v>19.73248</v>
+      </c>
+      <c r="G66">
+        <v>4.6</v>
+      </c>
+      <c r="H66">
+        <v>30.5</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>3.25</v>
+      </c>
+      <c r="K66">
+        <v>0.461</v>
+      </c>
+      <c r="L66">
+        <v>2.789</v>
+      </c>
+      <c r="M66">
+        <v>1.799602176</v>
+      </c>
+      <c r="N66">
+        <v>0.9893978239999999</v>
+      </c>
+      <c r="O66">
+        <v>0.1484096736</v>
+      </c>
+      <c r="P66">
+        <v>0.8409881503999999</v>
+      </c>
+      <c r="Q66">
+        <v>1.3019881504</v>
+      </c>
+      <c r="R66">
+        <v>1.777777777777778</v>
+      </c>
+      <c r="S66">
+        <v>0.4815071164593338</v>
+      </c>
+      <c r="T66">
+        <v>2.491745798578505</v>
+      </c>
+      <c r="U66">
+        <v>0.0912</v>
+      </c>
+      <c r="V66">
+        <v>0.15</v>
+      </c>
+      <c r="W66">
+        <v>0.07752000000000001</v>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y66">
+        <v>1.549786968028205</v>
+      </c>
+      <c r="Z66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>0.65</v>
+      </c>
+      <c r="B67">
+        <v>0.2230781129841123</v>
+      </c>
+      <c r="C67">
+        <v>9.752933937172298</v>
+      </c>
+      <c r="D67">
+        <v>25.1937339371723</v>
+      </c>
+      <c r="E67">
+        <v>19.7088</v>
+      </c>
+      <c r="F67">
+        <v>20.0408</v>
+      </c>
+      <c r="G67">
+        <v>4.6</v>
+      </c>
+      <c r="H67">
+        <v>30.5</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>3.25</v>
+      </c>
+      <c r="K67">
+        <v>0.461</v>
+      </c>
+      <c r="L67">
+        <v>2.789</v>
+      </c>
+      <c r="M67">
+        <v>1.82772096</v>
+      </c>
+      <c r="N67">
+        <v>0.96127904</v>
+      </c>
+      <c r="O67">
+        <v>0.144191856</v>
+      </c>
+      <c r="P67">
+        <v>0.817087184</v>
+      </c>
+      <c r="Q67">
+        <v>1.278087184</v>
+      </c>
+      <c r="R67">
+        <v>1.857142857142857</v>
+      </c>
+      <c r="S67">
+        <v>0.4934003228117495</v>
+      </c>
+      <c r="T67">
+        <v>2.558685872181278</v>
+      </c>
+      <c r="U67">
+        <v>0.0912</v>
+      </c>
+      <c r="V67">
+        <v>0.15</v>
+      </c>
+      <c r="W67">
+        <v>0.07752000000000001</v>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y67">
+        <v>1.525944091597002</v>
+      </c>
+      <c r="Z67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>0.66</v>
+      </c>
+      <c r="B68">
+        <v>0.2232008640428645</v>
+      </c>
+      <c r="C68">
+        <v>9.427843096478252</v>
+      </c>
+      <c r="D68">
+        <v>25.17696309647825</v>
+      </c>
+      <c r="E68">
+        <v>20.01712</v>
+      </c>
+      <c r="F68">
+        <v>20.34912</v>
+      </c>
+      <c r="G68">
+        <v>4.6</v>
+      </c>
+      <c r="H68">
+        <v>30.5</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>3.25</v>
+      </c>
+      <c r="K68">
+        <v>0.461</v>
+      </c>
+      <c r="L68">
+        <v>2.789</v>
+      </c>
+      <c r="M68">
+        <v>1.855839744</v>
+      </c>
+      <c r="N68">
+        <v>0.9331602559999999</v>
+      </c>
+      <c r="O68">
+        <v>0.1399740384</v>
+      </c>
+      <c r="P68">
+        <v>0.7931862175999999</v>
+      </c>
+      <c r="Q68">
+        <v>1.2541862176</v>
+      </c>
+      <c r="R68">
+        <v>1.941176470588236</v>
+      </c>
+      <c r="S68">
+        <v>0.5059931295378368</v>
+      </c>
+      <c r="T68">
+        <v>2.629563597172449</v>
+      </c>
+      <c r="U68">
+        <v>0.0912</v>
+      </c>
+      <c r="V68">
+        <v>0.15</v>
+      </c>
+      <c r="W68">
+        <v>0.07752000000000001</v>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y68">
+        <v>1.502823726572805</v>
+      </c>
+      <c r="Z68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>0.67</v>
+      </c>
+      <c r="B69">
+        <v>0.2651810480447678</v>
+      </c>
+      <c r="C69">
+        <v>4.450697889916462</v>
+      </c>
+      <c r="D69">
+        <v>20.50813788991647</v>
+      </c>
+      <c r="E69">
+        <v>20.32544</v>
+      </c>
+      <c r="F69">
+        <v>20.65744</v>
+      </c>
+      <c r="G69">
+        <v>4.6</v>
+      </c>
+      <c r="H69">
+        <v>30.5</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>3.25</v>
+      </c>
+      <c r="K69">
+        <v>0.461</v>
+      </c>
+      <c r="L69">
+        <v>2.789</v>
+      </c>
+      <c r="M69">
+        <v>3.234955104</v>
+      </c>
+      <c r="N69">
+        <v>-0.4459551040000003</v>
+      </c>
+      <c r="O69">
+        <v>-0.06689326560000004</v>
+      </c>
+      <c r="P69">
+        <v>-0.3790618384000002</v>
+      </c>
+      <c r="Q69">
+        <v>0.08193816159999978</v>
+      </c>
+      <c r="R69">
+        <v>2.030303030303031</v>
+      </c>
+      <c r="S69">
+        <v>0.5267507360825707</v>
+      </c>
+      <c r="T69">
+        <v>2.746396322406352</v>
+      </c>
+      <c r="U69">
+        <v>0.1566</v>
+      </c>
+      <c r="V69">
+        <v>0.1293217329299912</v>
+      </c>
+      <c r="W69">
+        <v>0.1363482166231634</v>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y69">
+        <v>0.8621448861999415</v>
+      </c>
+      <c r="Z69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>0.68</v>
+      </c>
+      <c r="B70">
+        <v>0.2663590480447678</v>
+      </c>
+      <c r="C70">
+        <v>4.036213856264986</v>
+      </c>
+      <c r="D70">
+        <v>20.40197385626499</v>
+      </c>
+      <c r="E70">
+        <v>20.63376</v>
+      </c>
+      <c r="F70">
+        <v>20.96576</v>
+      </c>
+      <c r="G70">
+        <v>4.6</v>
+      </c>
+      <c r="H70">
+        <v>30.5</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>3.25</v>
+      </c>
+      <c r="K70">
+        <v>0.461</v>
+      </c>
+      <c r="L70">
+        <v>2.789</v>
+      </c>
+      <c r="M70">
+        <v>3.283238016000001</v>
+      </c>
+      <c r="N70">
+        <v>-0.4942380160000006</v>
+      </c>
+      <c r="O70">
+        <v>-0.07413570240000009</v>
+      </c>
+      <c r="P70">
+        <v>-0.4201023136000005</v>
+      </c>
+      <c r="Q70">
+        <v>0.04089768639999952</v>
+      </c>
+      <c r="R70">
+        <v>2.125</v>
+      </c>
+      <c r="S70">
+        <v>0.5419991965851512</v>
+      </c>
+      <c r="T70">
+        <v>2.83222120748155</v>
+      </c>
+      <c r="U70">
+        <v>0.1566</v>
+      </c>
+      <c r="V70">
+        <v>0.1274199427398443</v>
+      </c>
+      <c r="W70">
+        <v>0.1366460369669404</v>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y70">
+        <v>0.8494662849322951</v>
+      </c>
+      <c r="Z70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>0.6900000000000001</v>
+      </c>
+      <c r="B71">
+        <v>0.2675370480447678</v>
+      </c>
+      <c r="C71">
+        <v>3.622823316061218</v>
+      </c>
+      <c r="D71">
+        <v>20.29690331606122</v>
+      </c>
+      <c r="E71">
+        <v>20.94208</v>
+      </c>
+      <c r="F71">
+        <v>21.27408</v>
+      </c>
+      <c r="G71">
+        <v>4.6</v>
+      </c>
+      <c r="H71">
+        <v>30.5</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>3.25</v>
+      </c>
+      <c r="K71">
+        <v>0.461</v>
+      </c>
+      <c r="L71">
+        <v>2.789</v>
+      </c>
+      <c r="M71">
+        <v>3.331520928000001</v>
+      </c>
+      <c r="N71">
+        <v>-0.5425209280000005</v>
+      </c>
+      <c r="O71">
+        <v>-0.08137813920000007</v>
+      </c>
+      <c r="P71">
+        <v>-0.4611427888000004</v>
+      </c>
+      <c r="Q71">
+        <v>-0.0001427888000004041</v>
+      </c>
+      <c r="R71">
+        <v>2.225806451612904</v>
+      </c>
+      <c r="S71">
+        <v>0.5582314287330592</v>
+      </c>
+      <c r="T71">
+        <v>2.923583181916439</v>
+      </c>
+      <c r="U71">
+        <v>0.1566</v>
+      </c>
+      <c r="V71">
+        <v>0.1255732769030349</v>
+      </c>
+      <c r="W71">
+        <v>0.1369352248369848</v>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y71">
+        <v>0.8371551793535663</v>
+      </c>
+      <c r="Z71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>0.7000000000000001</v>
+      </c>
+      <c r="B72">
+        <v>0.2687150480447678</v>
+      </c>
+      <c r="C72">
+        <v>3.210509461332475</v>
+      </c>
+      <c r="D72">
+        <v>20.19290946133248</v>
+      </c>
+      <c r="E72">
+        <v>21.2504</v>
+      </c>
+      <c r="F72">
+        <v>21.5824</v>
+      </c>
+      <c r="G72">
+        <v>4.6</v>
+      </c>
+      <c r="H72">
+        <v>30.5</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="J72">
+        <v>3.25</v>
+      </c>
+      <c r="K72">
+        <v>0.461</v>
+      </c>
+      <c r="L72">
+        <v>2.789</v>
+      </c>
+      <c r="M72">
+        <v>3.379803840000001</v>
+      </c>
+      <c r="N72">
+        <v>-0.5908038400000009</v>
+      </c>
+      <c r="O72">
+        <v>-0.08862057600000013</v>
+      </c>
+      <c r="P72">
+        <v>-0.5021832640000007</v>
+      </c>
+      <c r="Q72">
+        <v>-0.04118326400000066</v>
+      </c>
+      <c r="R72">
+        <v>2.333333333333334</v>
+      </c>
+      <c r="S72">
+        <v>0.5755458096908279</v>
+      </c>
+      <c r="T72">
+        <v>3.021035954646987</v>
+      </c>
+      <c r="U72">
+        <v>0.1566</v>
+      </c>
+      <c r="V72">
+        <v>0.1237793729472773</v>
+      </c>
+      <c r="W72">
+        <v>0.1372161501964564</v>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y72">
+        <v>0.8251958196485153</v>
+      </c>
+      <c r="Z72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>0.71</v>
+      </c>
+      <c r="B73">
+        <v>0.2698930480447678</v>
+      </c>
+      <c r="C73">
+        <v>2.799255826821582</v>
+      </c>
+      <c r="D73">
+        <v>20.08997582682158</v>
+      </c>
+      <c r="E73">
+        <v>21.55872</v>
+      </c>
+      <c r="F73">
+        <v>21.89072</v>
+      </c>
+      <c r="G73">
+        <v>4.6</v>
+      </c>
+      <c r="H73">
+        <v>30.5</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>3.25</v>
+      </c>
+      <c r="K73">
+        <v>0.461</v>
+      </c>
+      <c r="L73">
+        <v>2.789</v>
+      </c>
+      <c r="M73">
+        <v>3.428086752</v>
+      </c>
+      <c r="N73">
+        <v>-0.6390867519999999</v>
+      </c>
+      <c r="O73">
+        <v>-0.09586301279999998</v>
+      </c>
+      <c r="P73">
+        <v>-0.5432237391999999</v>
+      </c>
+      <c r="Q73">
+        <v>-0.08222373919999987</v>
+      </c>
+      <c r="R73">
+        <v>2.448275862068965</v>
+      </c>
+      <c r="S73">
+        <v>0.5940542858870632</v>
+      </c>
+      <c r="T73">
+        <v>3.125209608255503</v>
+      </c>
+      <c r="U73">
+        <v>0.1566</v>
+      </c>
+      <c r="V73">
+        <v>0.1220360014973157</v>
+      </c>
+      <c r="W73">
+        <v>0.1374891621655204</v>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y73">
+        <v>0.8135733433154378</v>
+      </c>
+      <c r="Z73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>0.72</v>
+      </c>
+      <c r="B74">
+        <v>0.2710710480447677</v>
+      </c>
+      <c r="C74">
+        <v>2.389046281296157</v>
+      </c>
+      <c r="D74">
+        <v>19.98808628129616</v>
+      </c>
+      <c r="E74">
+        <v>21.86704</v>
+      </c>
+      <c r="F74">
+        <v>22.19904</v>
+      </c>
+      <c r="G74">
+        <v>4.6</v>
+      </c>
+      <c r="H74">
+        <v>30.5</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="J74">
+        <v>3.25</v>
+      </c>
+      <c r="K74">
+        <v>0.461</v>
+      </c>
+      <c r="L74">
+        <v>2.789</v>
+      </c>
+      <c r="M74">
+        <v>3.476369664</v>
+      </c>
+      <c r="N74">
+        <v>-0.6873696640000002</v>
+      </c>
+      <c r="O74">
+        <v>-0.1031054496</v>
+      </c>
+      <c r="P74">
+        <v>-0.5842642144000002</v>
+      </c>
+      <c r="Q74">
+        <v>-0.1232642144000002</v>
+      </c>
+      <c r="R74">
+        <v>2.571428571428571</v>
+      </c>
+      <c r="S74">
+        <v>0.6138847960973153</v>
+      </c>
+      <c r="T74">
+        <v>3.236824237121771</v>
+      </c>
+      <c r="U74">
+        <v>0.1566</v>
+      </c>
+      <c r="V74">
+        <v>0.1203410570320752</v>
+      </c>
+      <c r="W74">
+        <v>0.137754590468777</v>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y74">
+        <v>0.8022737135471678</v>
+      </c>
+      <c r="Z74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>0.73</v>
+      </c>
+      <c r="B75">
+        <v>0.314173935859261</v>
+      </c>
+      <c r="C75">
+        <v>-1.04790765394106</v>
+      </c>
+      <c r="D75">
+        <v>16.85945234605894</v>
+      </c>
+      <c r="E75">
+        <v>22.17536</v>
+      </c>
+      <c r="F75">
+        <v>22.50736</v>
+      </c>
+      <c r="G75">
+        <v>4.6</v>
+      </c>
+      <c r="H75">
+        <v>30.5</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>3.25</v>
+      </c>
+      <c r="K75">
+        <v>0.461</v>
+      </c>
+      <c r="L75">
+        <v>2.789</v>
+      </c>
+      <c r="M75">
+        <v>4.699536768</v>
+      </c>
+      <c r="N75">
+        <v>-1.910536768</v>
+      </c>
+      <c r="O75">
+        <v>-0.2865805151999999</v>
+      </c>
+      <c r="P75">
+        <v>-1.6239562528</v>
+      </c>
+      <c r="Q75">
+        <v>-1.1629562528</v>
+      </c>
+      <c r="R75">
+        <v>2.703703703703703</v>
+      </c>
+      <c r="S75">
+        <v>0.6493282619323761</v>
+      </c>
+      <c r="T75">
+        <v>3.436315286165447</v>
+      </c>
+      <c r="U75">
+        <v>0.2088</v>
+      </c>
+      <c r="V75">
+        <v>0.0890194120511241</v>
+      </c>
+      <c r="W75">
+        <v>0.1902127467637253</v>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y75">
+        <v>0.593462747007494</v>
+      </c>
+      <c r="Z75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>0.74</v>
+      </c>
+      <c r="B76">
+        <v>0.315873935859261</v>
+      </c>
+      <c r="C76">
+        <v>-1.459669606715927</v>
+      </c>
+      <c r="D76">
+        <v>16.75601039328407</v>
+      </c>
+      <c r="E76">
+        <v>22.48368</v>
+      </c>
+      <c r="F76">
+        <v>22.81568</v>
+      </c>
+      <c r="G76">
+        <v>4.6</v>
+      </c>
+      <c r="H76">
+        <v>30.5</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>3.25</v>
+      </c>
+      <c r="K76">
+        <v>0.461</v>
+      </c>
+      <c r="L76">
+        <v>2.789</v>
+      </c>
+      <c r="M76">
+        <v>4.763913984</v>
+      </c>
+      <c r="N76">
+        <v>-1.974913984</v>
+      </c>
+      <c r="O76">
+        <v>-0.2962370976</v>
+      </c>
+      <c r="P76">
+        <v>-1.6786768864</v>
+      </c>
+      <c r="Q76">
+        <v>-1.2176768864</v>
+      </c>
+      <c r="R76">
+        <v>2.846153846153846</v>
+      </c>
+      <c r="S76">
+        <v>0.6728101181605446</v>
+      </c>
+      <c r="T76">
+        <v>3.568481258710272</v>
+      </c>
+      <c r="U76">
+        <v>0.2088</v>
+      </c>
+      <c r="V76">
+        <v>0.0878164470234062</v>
+      </c>
+      <c r="W76">
+        <v>0.1904639258615128</v>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y76">
+        <v>0.5854429801560415</v>
+      </c>
+      <c r="Z76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>0.75</v>
+      </c>
+      <c r="B77">
+        <v>0.3175739358592611</v>
+      </c>
+      <c r="C77">
+        <v>-1.870169954318314</v>
+      </c>
+      <c r="D77">
+        <v>16.65383004568169</v>
+      </c>
+      <c r="E77">
+        <v>22.792</v>
+      </c>
+      <c r="F77">
+        <v>23.124</v>
+      </c>
+      <c r="G77">
+        <v>4.6</v>
+      </c>
+      <c r="H77">
+        <v>30.5</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <v>3.25</v>
+      </c>
+      <c r="K77">
+        <v>0.461</v>
+      </c>
+      <c r="L77">
+        <v>2.789</v>
+      </c>
+      <c r="M77">
+        <v>4.828291200000001</v>
+      </c>
+      <c r="N77">
+        <v>-2.039291200000001</v>
+      </c>
+      <c r="O77">
+        <v>-0.3058936800000001</v>
+      </c>
+      <c r="P77">
+        <v>-1.73339752</v>
+      </c>
+      <c r="Q77">
+        <v>-1.27239752</v>
+      </c>
+      <c r="R77">
+        <v>3</v>
+      </c>
+      <c r="S77">
+        <v>0.6981705228869663</v>
+      </c>
+      <c r="T77">
+        <v>3.711220509058684</v>
+      </c>
+      <c r="U77">
+        <v>0.2088</v>
+      </c>
+      <c r="V77">
+        <v>0.08664556106309411</v>
+      </c>
+      <c r="W77">
+        <v>0.190708406850026</v>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y77">
+        <v>0.5776370737539608</v>
+      </c>
+      <c r="Z77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>0.76</v>
+      </c>
+      <c r="B78">
+        <v>0.3192739358592611</v>
+      </c>
+      <c r="C78">
+        <v>-2.279431637155692</v>
+      </c>
+      <c r="D78">
+        <v>16.55288836284431</v>
+      </c>
+      <c r="E78">
+        <v>23.10032</v>
+      </c>
+      <c r="F78">
+        <v>23.43232</v>
+      </c>
+      <c r="G78">
+        <v>4.6</v>
+      </c>
+      <c r="H78">
+        <v>30.5</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78">
+        <v>3.25</v>
+      </c>
+      <c r="K78">
+        <v>0.461</v>
+      </c>
+      <c r="L78">
+        <v>2.789</v>
+      </c>
+      <c r="M78">
+        <v>4.892668416</v>
+      </c>
+      <c r="N78">
+        <v>-2.103668416</v>
+      </c>
+      <c r="O78">
+        <v>-0.3155502624</v>
+      </c>
+      <c r="P78">
+        <v>-1.7881181536</v>
+      </c>
+      <c r="Q78">
+        <v>-1.3271181536</v>
+      </c>
+      <c r="R78">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="S78">
+        <v>0.7256442946739234</v>
+      </c>
+      <c r="T78">
+        <v>3.865854696936129</v>
+      </c>
+      <c r="U78">
+        <v>0.2088</v>
+      </c>
+      <c r="V78">
+        <v>0.0855054878912113</v>
+      </c>
+      <c r="W78">
+        <v>0.1909464541283151</v>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y78">
+        <v>0.5700365859414087</v>
+      </c>
+      <c r="Z78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>0.77</v>
+      </c>
+      <c r="B79">
+        <v>0.320973935859261</v>
+      </c>
+      <c r="C79">
+        <v>-2.687477042803618</v>
+      </c>
+      <c r="D79">
+        <v>16.45316295719639</v>
+      </c>
+      <c r="E79">
+        <v>23.40864</v>
+      </c>
+      <c r="F79">
+        <v>23.74064</v>
+      </c>
+      <c r="G79">
+        <v>4.6</v>
+      </c>
+      <c r="H79">
+        <v>30.5</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <v>3.25</v>
+      </c>
+      <c r="K79">
+        <v>0.461</v>
+      </c>
+      <c r="L79">
+        <v>2.789</v>
+      </c>
+      <c r="M79">
+        <v>4.957045632000001</v>
+      </c>
+      <c r="N79">
+        <v>-2.168045632000001</v>
+      </c>
+      <c r="O79">
+        <v>-0.3252068448000001</v>
+      </c>
+      <c r="P79">
+        <v>-1.8428387872</v>
+      </c>
+      <c r="Q79">
+        <v>-1.3818387872</v>
+      </c>
+      <c r="R79">
+        <v>3.347826086956522</v>
+      </c>
+      <c r="S79">
+        <v>0.7555070900945287</v>
+      </c>
+      <c r="T79">
+        <v>4.033935335933352</v>
+      </c>
+      <c r="U79">
+        <v>0.2088</v>
+      </c>
+      <c r="V79">
+        <v>0.08439502700950725</v>
+      </c>
+      <c r="W79">
+        <v>0.1911783183604149</v>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y79">
+        <v>0.5626335133967151</v>
+      </c>
+      <c r="Z79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>0.78</v>
+      </c>
+      <c r="B80">
+        <v>0.3226739358592611</v>
+      </c>
+      <c r="C80">
+        <v>-3.094328022559019</v>
+      </c>
+      <c r="D80">
+        <v>16.35463197744098</v>
+      </c>
+      <c r="E80">
+        <v>23.71696</v>
+      </c>
+      <c r="F80">
+        <v>24.04896</v>
+      </c>
+      <c r="G80">
+        <v>4.6</v>
+      </c>
+      <c r="H80">
+        <v>30.5</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <v>3.25</v>
+      </c>
+      <c r="K80">
+        <v>0.461</v>
+      </c>
+      <c r="L80">
+        <v>2.789</v>
+      </c>
+      <c r="M80">
+        <v>5.021422848</v>
+      </c>
+      <c r="N80">
+        <v>-2.232422848</v>
+      </c>
+      <c r="O80">
+        <v>-0.3348634272</v>
+      </c>
+      <c r="P80">
+        <v>-1.8975594208</v>
+      </c>
+      <c r="Q80">
+        <v>-1.4365594208</v>
+      </c>
+      <c r="R80">
+        <v>3.545454545454546</v>
+      </c>
+      <c r="S80">
+        <v>0.7880846850988257</v>
+      </c>
+      <c r="T80">
+        <v>4.217296033021232</v>
+      </c>
+      <c r="U80">
+        <v>0.2088</v>
+      </c>
+      <c r="V80">
+        <v>0.08331303948374434</v>
+      </c>
+      <c r="W80">
+        <v>0.1914042373557942</v>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y80">
+        <v>0.5554202632249623</v>
+      </c>
+      <c r="Z80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>0.79</v>
+      </c>
+      <c r="B81">
+        <v>0.3243739358592611</v>
+      </c>
+      <c r="C81">
+        <v>-3.500005907402375</v>
+      </c>
+      <c r="D81">
+        <v>16.25727409259763</v>
+      </c>
+      <c r="E81">
+        <v>24.02528</v>
+      </c>
+      <c r="F81">
+        <v>24.35728</v>
+      </c>
+      <c r="G81">
+        <v>4.6</v>
+      </c>
+      <c r="H81">
+        <v>30.5</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="J81">
+        <v>3.25</v>
+      </c>
+      <c r="K81">
+        <v>0.461</v>
+      </c>
+      <c r="L81">
+        <v>2.789</v>
+      </c>
+      <c r="M81">
+        <v>5.085800064000001</v>
+      </c>
+      <c r="N81">
+        <v>-2.296800064000001</v>
+      </c>
+      <c r="O81">
+        <v>-0.3445200096000001</v>
+      </c>
+      <c r="P81">
+        <v>-1.952280054400001</v>
+      </c>
+      <c r="Q81">
+        <v>-1.4912800544</v>
+      </c>
+      <c r="R81">
+        <v>3.761904761904763</v>
+      </c>
+      <c r="S81">
+        <v>0.8237649081987697</v>
+      </c>
+      <c r="T81">
+        <v>4.41811965364129</v>
+      </c>
+      <c r="U81">
+        <v>0.2088</v>
+      </c>
+      <c r="V81">
+        <v>0.08225844404724124</v>
+      </c>
+      <c r="W81">
+        <v>0.191624436882936</v>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y81">
+        <v>0.5483896269816083</v>
+      </c>
+      <c r="Z81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>0.8</v>
+      </c>
+      <c r="B82">
+        <v>0.326073935859261</v>
+      </c>
+      <c r="C82">
+        <v>-3.904531523393079</v>
+      </c>
+      <c r="D82">
+        <v>16.16106847660692</v>
+      </c>
+      <c r="E82">
+        <v>24.3336</v>
+      </c>
+      <c r="F82">
+        <v>24.6656</v>
+      </c>
+      <c r="G82">
+        <v>4.6</v>
+      </c>
+      <c r="H82">
+        <v>30.5</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <v>3.25</v>
+      </c>
+      <c r="K82">
+        <v>0.461</v>
+      </c>
+      <c r="L82">
+        <v>2.789</v>
+      </c>
+      <c r="M82">
+        <v>5.15017728</v>
+      </c>
+      <c r="N82">
+        <v>-2.36117728</v>
+      </c>
+      <c r="O82">
+        <v>-0.354176592</v>
+      </c>
+      <c r="P82">
+        <v>-2.007000688</v>
+      </c>
+      <c r="Q82">
+        <v>-1.546000688</v>
+      </c>
+      <c r="R82">
+        <v>4.000000000000001</v>
+      </c>
+      <c r="S82">
+        <v>0.863013153608708</v>
+      </c>
+      <c r="T82">
+        <v>4.639025636323355</v>
+      </c>
+      <c r="U82">
+        <v>0.2088</v>
+      </c>
+      <c r="V82">
+        <v>0.08123021349665073</v>
+      </c>
+      <c r="W82">
+        <v>0.1918391314218993</v>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y82">
+        <v>0.5415347566443383</v>
+      </c>
+      <c r="Z82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="B83">
+        <v>0.3277739358592611</v>
+      </c>
+      <c r="C83">
+        <v>-4.307925206521414</v>
+      </c>
+      <c r="D83">
+        <v>16.06599479347859</v>
+      </c>
+      <c r="E83">
+        <v>24.64192</v>
+      </c>
+      <c r="F83">
+        <v>24.97392</v>
+      </c>
+      <c r="G83">
+        <v>4.6</v>
+      </c>
+      <c r="H83">
+        <v>30.5</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="J83">
+        <v>3.25</v>
+      </c>
+      <c r="K83">
+        <v>0.461</v>
+      </c>
+      <c r="L83">
+        <v>2.789</v>
+      </c>
+      <c r="M83">
+        <v>5.214554496000001</v>
+      </c>
+      <c r="N83">
+        <v>-2.425554496000001</v>
+      </c>
+      <c r="O83">
+        <v>-0.3638331744000001</v>
+      </c>
+      <c r="P83">
+        <v>-2.0617213216</v>
+      </c>
+      <c r="Q83">
+        <v>-1.6007213216</v>
+      </c>
+      <c r="R83">
+        <v>4.263157894736843</v>
+      </c>
+      <c r="S83">
+        <v>0.9063927932723244</v>
+      </c>
+      <c r="T83">
+        <v>4.883184880340374</v>
+      </c>
+      <c r="U83">
+        <v>0.2088</v>
+      </c>
+      <c r="V83">
+        <v>0.08022737135471678</v>
+      </c>
+      <c r="W83">
+        <v>0.1920485248611351</v>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y83">
+        <v>0.5348491423647785</v>
+      </c>
+      <c r="Z83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>0.8200000000000001</v>
+      </c>
+      <c r="B84">
+        <v>0.3294739358592611</v>
+      </c>
+      <c r="C84">
+        <v>-4.710206817039321</v>
+      </c>
+      <c r="D84">
+        <v>15.97203318296068</v>
+      </c>
+      <c r="E84">
+        <v>24.95024</v>
+      </c>
+      <c r="F84">
+        <v>25.28224</v>
+      </c>
+      <c r="G84">
+        <v>4.6</v>
+      </c>
+      <c r="H84">
+        <v>30.5</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="J84">
+        <v>3.25</v>
+      </c>
+      <c r="K84">
+        <v>0.461</v>
+      </c>
+      <c r="L84">
+        <v>2.789</v>
+      </c>
+      <c r="M84">
+        <v>5.278931712</v>
+      </c>
+      <c r="N84">
+        <v>-2.489931712</v>
+      </c>
+      <c r="O84">
+        <v>-0.3734897568</v>
+      </c>
+      <c r="P84">
+        <v>-2.1164419552</v>
+      </c>
+      <c r="Q84">
+        <v>-1.6554419552</v>
+      </c>
+      <c r="R84">
+        <v>4.555555555555557</v>
+      </c>
+      <c r="S84">
+        <v>0.9545923928985647</v>
+      </c>
+      <c r="T84">
+        <v>5.154472929248173</v>
+      </c>
+      <c r="U84">
+        <v>0.2088</v>
+      </c>
+      <c r="V84">
+        <v>0.07924898877722024</v>
+      </c>
+      <c r="W84">
+        <v>0.1922528111433164</v>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y84">
+        <v>0.5283265918481349</v>
+      </c>
+      <c r="Z84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>0.8300000000000001</v>
+      </c>
+      <c r="B85">
+        <v>0.3311739358592611</v>
+      </c>
+      <c r="C85">
+        <v>-5.11139575329123</v>
+      </c>
+      <c r="D85">
+        <v>15.87916424670877</v>
+      </c>
+      <c r="E85">
+        <v>25.25856</v>
+      </c>
+      <c r="F85">
+        <v>25.59056</v>
+      </c>
+      <c r="G85">
+        <v>4.6</v>
+      </c>
+      <c r="H85">
+        <v>30.5</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="J85">
+        <v>3.25</v>
+      </c>
+      <c r="K85">
+        <v>0.461</v>
+      </c>
+      <c r="L85">
+        <v>2.789</v>
+      </c>
+      <c r="M85">
+        <v>5.343308928000001</v>
+      </c>
+      <c r="N85">
+        <v>-2.554308928000001</v>
+      </c>
+      <c r="O85">
+        <v>-0.3831463392000001</v>
+      </c>
+      <c r="P85">
+        <v>-2.171162588800001</v>
+      </c>
+      <c r="Q85">
+        <v>-1.7101625888</v>
+      </c>
+      <c r="R85">
+        <v>4.882352941176473</v>
+      </c>
+      <c r="S85">
+        <v>1.008462533657304</v>
+      </c>
+      <c r="T85">
+        <v>5.457677219203948</v>
+      </c>
+      <c r="U85">
+        <v>0.2088</v>
+      </c>
+      <c r="V85">
+        <v>0.07829418168351877</v>
+      </c>
+      <c r="W85">
+        <v>0.1924521748644813</v>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y85">
+        <v>0.5219612112234585</v>
+      </c>
+      <c r="Z85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>0.84</v>
+      </c>
+      <c r="B86">
+        <v>0.332873935859261</v>
+      </c>
+      <c r="C86">
+        <v>-5.511510965065188</v>
+      </c>
+      <c r="D86">
+        <v>15.78736903493481</v>
+      </c>
+      <c r="E86">
+        <v>25.56688</v>
+      </c>
+      <c r="F86">
+        <v>25.89888</v>
+      </c>
+      <c r="G86">
+        <v>4.6</v>
+      </c>
+      <c r="H86">
+        <v>30.5</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="J86">
+        <v>3.25</v>
+      </c>
+      <c r="K86">
+        <v>0.461</v>
+      </c>
+      <c r="L86">
+        <v>2.789</v>
+      </c>
+      <c r="M86">
+        <v>5.407686144</v>
+      </c>
+      <c r="N86">
+        <v>-2.618686144</v>
+      </c>
+      <c r="O86">
+        <v>-0.3928029216</v>
+      </c>
+      <c r="P86">
+        <v>-2.2258832224</v>
+      </c>
+      <c r="Q86">
+        <v>-1.7648832224</v>
+      </c>
+      <c r="R86">
+        <v>5.249999999999999</v>
+      </c>
+      <c r="S86">
+        <v>1.069066442010885</v>
+      </c>
+      <c r="T86">
+        <v>5.798782045404192</v>
+      </c>
+      <c r="U86">
+        <v>0.2088</v>
+      </c>
+      <c r="V86">
+        <v>0.07736210809204831</v>
+      </c>
+      <c r="W86">
+        <v>0.1926467918303803</v>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y86">
+        <v>0.5157473872803222</v>
+      </c>
+      <c r="Z86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>0.85</v>
+      </c>
+      <c r="B87">
+        <v>0.3345739358592611</v>
+      </c>
+      <c r="C87">
+        <v>-5.910570966483576</v>
+      </c>
+      <c r="D87">
+        <v>15.69662903351642</v>
+      </c>
+      <c r="E87">
+        <v>25.8752</v>
+      </c>
+      <c r="F87">
+        <v>26.2072</v>
+      </c>
+      <c r="G87">
+        <v>4.6</v>
+      </c>
+      <c r="H87">
+        <v>30.5</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+      <c r="J87">
+        <v>3.25</v>
+      </c>
+      <c r="K87">
+        <v>0.461</v>
+      </c>
+      <c r="L87">
+        <v>2.789</v>
+      </c>
+      <c r="M87">
+        <v>5.472063360000001</v>
+      </c>
+      <c r="N87">
+        <v>-2.683063360000001</v>
+      </c>
+      <c r="O87">
+        <v>-0.4024595040000001</v>
+      </c>
+      <c r="P87">
+        <v>-2.280603856000001</v>
+      </c>
+      <c r="Q87">
+        <v>-1.819603856000001</v>
+      </c>
+      <c r="R87">
+        <v>5.666666666666666</v>
+      </c>
+      <c r="S87">
+        <v>1.137750871478277</v>
+      </c>
+      <c r="T87">
+        <v>6.185367515097805</v>
+      </c>
+      <c r="U87">
+        <v>0.2088</v>
+      </c>
+      <c r="V87">
+        <v>0.07645196564390656</v>
+      </c>
+      <c r="W87">
+        <v>0.1928368295735523</v>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y87">
+        <v>0.5096797709593772</v>
+      </c>
+      <c r="Z87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>0.86</v>
+      </c>
+      <c r="B88">
+        <v>0.336273935859261</v>
+      </c>
+      <c r="C88">
+        <v>-6.308593848451697</v>
+      </c>
+      <c r="D88">
+        <v>15.6069261515483</v>
+      </c>
+      <c r="E88">
+        <v>26.18352</v>
+      </c>
+      <c r="F88">
+        <v>26.51552</v>
+      </c>
+      <c r="G88">
+        <v>4.6</v>
+      </c>
+      <c r="H88">
+        <v>30.5</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+      <c r="J88">
+        <v>3.25</v>
+      </c>
+      <c r="K88">
+        <v>0.461</v>
+      </c>
+      <c r="L88">
+        <v>2.789</v>
+      </c>
+      <c r="M88">
+        <v>5.536440576</v>
+      </c>
+      <c r="N88">
+        <v>-2.747440576</v>
+      </c>
+      <c r="O88">
+        <v>-0.4121160864</v>
+      </c>
+      <c r="P88">
+        <v>-2.3353244896</v>
+      </c>
+      <c r="Q88">
+        <v>-1.8743244896</v>
+      </c>
+      <c r="R88">
+        <v>6.142857142857142</v>
+      </c>
+      <c r="S88">
+        <v>1.216247362298154</v>
+      </c>
+      <c r="T88">
+        <v>6.627179480461934</v>
+      </c>
+      <c r="U88">
+        <v>0.2088</v>
+      </c>
+      <c r="V88">
+        <v>0.07556298929920999</v>
+      </c>
+      <c r="W88">
+        <v>0.193022447834325</v>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y88">
+        <v>0.5037532619947332</v>
+      </c>
+      <c r="Z88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>0.87</v>
+      </c>
+      <c r="B89">
+        <v>0.3655132151863314</v>
+      </c>
+      <c r="C89">
+        <v>-8.013659532343983</v>
+      </c>
+      <c r="D89">
+        <v>14.21018046765602</v>
+      </c>
+      <c r="E89">
+        <v>26.49184</v>
+      </c>
+      <c r="F89">
+        <v>26.82384</v>
+      </c>
+      <c r="G89">
+        <v>4.6</v>
+      </c>
+      <c r="H89">
+        <v>30.5</v>
+      </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
+      <c r="J89">
+        <v>3.25</v>
+      </c>
+      <c r="K89">
+        <v>0.461</v>
+      </c>
+      <c r="L89">
+        <v>2.789</v>
+      </c>
+      <c r="M89">
+        <v>6.405532992</v>
+      </c>
+      <c r="N89">
+        <v>-3.616532992</v>
+      </c>
+      <c r="O89">
+        <v>-0.5424799488000001</v>
+      </c>
+      <c r="P89">
+        <v>-3.0740530432</v>
+      </c>
+      <c r="Q89">
+        <v>-2.6130530432</v>
+      </c>
+      <c r="R89">
+        <v>6.692307692307692</v>
+      </c>
+      <c r="S89">
+        <v>1.317891615760092</v>
+      </c>
+      <c r="T89">
+        <v>7.199276996171728</v>
+      </c>
+      <c r="U89">
+        <v>0.2388</v>
+      </c>
+      <c r="V89">
+        <v>0.06531072441941768</v>
+      </c>
+      <c r="W89">
+        <v>0.2232037990086431</v>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y89">
+        <v>0.4354048294627846</v>
+      </c>
+      <c r="Z89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>0.88</v>
+      </c>
+      <c r="B90">
+        <v>0.3675132151863314</v>
+      </c>
+      <c r="C90">
+        <v>-8.408438973651215</v>
+      </c>
+      <c r="D90">
+        <v>14.12372102634879</v>
+      </c>
+      <c r="E90">
+        <v>26.80016</v>
+      </c>
+      <c r="F90">
+        <v>27.13216</v>
+      </c>
+      <c r="G90">
+        <v>4.6</v>
+      </c>
+      <c r="H90">
+        <v>30.5</v>
+      </c>
+      <c r="I90">
+        <v>0</v>
+      </c>
+      <c r="J90">
+        <v>3.25</v>
+      </c>
+      <c r="K90">
+        <v>0.461</v>
+      </c>
+      <c r="L90">
+        <v>2.789</v>
+      </c>
+      <c r="M90">
+        <v>6.479159808000001</v>
+      </c>
+      <c r="N90">
+        <v>-3.690159808000001</v>
+      </c>
+      <c r="O90">
+        <v>-0.5535239712000002</v>
+      </c>
+      <c r="P90">
+        <v>-3.136635836800001</v>
+      </c>
+      <c r="Q90">
+        <v>-2.675635836800001</v>
+      </c>
+      <c r="R90">
+        <v>7.333333333333334</v>
+      </c>
+      <c r="S90">
+        <v>1.424482583740099</v>
+      </c>
+      <c r="T90">
+        <v>7.799216745852707</v>
+      </c>
+      <c r="U90">
+        <v>0.2388</v>
+      </c>
+      <c r="V90">
+        <v>0.06456855709646973</v>
+      </c>
+      <c r="W90">
+        <v>0.223381028565363</v>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y90">
+        <v>0.4304570473097983</v>
+      </c>
+      <c r="Z90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>0.89</v>
+      </c>
+      <c r="B91">
+        <v>0.3695132151863314</v>
+      </c>
+      <c r="C91">
+        <v>-8.80217268182971</v>
+      </c>
+      <c r="D91">
+        <v>14.03830731817029</v>
+      </c>
+      <c r="E91">
+        <v>27.10848</v>
+      </c>
+      <c r="F91">
+        <v>27.44048</v>
+      </c>
+      <c r="G91">
+        <v>4.6</v>
+      </c>
+      <c r="H91">
+        <v>30.5</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="J91">
+        <v>3.25</v>
+      </c>
+      <c r="K91">
+        <v>0.461</v>
+      </c>
+      <c r="L91">
+        <v>2.789</v>
+      </c>
+      <c r="M91">
+        <v>6.552786624</v>
+      </c>
+      <c r="N91">
+        <v>-3.763786624</v>
+      </c>
+      <c r="O91">
+        <v>-0.5645679936</v>
+      </c>
+      <c r="P91">
+        <v>-3.1992186304</v>
+      </c>
+      <c r="Q91">
+        <v>-2.7382186304</v>
+      </c>
+      <c r="R91">
+        <v>8.090909090909092</v>
+      </c>
+      <c r="S91">
+        <v>1.550453727716472</v>
+      </c>
+      <c r="T91">
+        <v>8.508236450021135</v>
+      </c>
+      <c r="U91">
+        <v>0.2388</v>
+      </c>
+      <c r="V91">
+        <v>0.06384306769089144</v>
+      </c>
+      <c r="W91">
+        <v>0.2235542754354151</v>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y91">
+        <v>0.4256204512726096</v>
+      </c>
+      <c r="Z91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <v>0.9</v>
+      </c>
+      <c r="B92">
+        <v>0.3715132151863314</v>
+      </c>
+      <c r="C92">
+        <v>-9.194879515158874</v>
+      </c>
+      <c r="D92">
+        <v>13.95392048484113</v>
+      </c>
+      <c r="E92">
+        <v>27.4168</v>
+      </c>
+      <c r="F92">
+        <v>27.7488</v>
+      </c>
+      <c r="G92">
+        <v>4.6</v>
+      </c>
+      <c r="H92">
+        <v>30.5</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+      <c r="J92">
+        <v>3.25</v>
+      </c>
+      <c r="K92">
+        <v>0.461</v>
+      </c>
+      <c r="L92">
+        <v>2.789</v>
+      </c>
+      <c r="M92">
+        <v>6.626413440000001</v>
+      </c>
+      <c r="N92">
+        <v>-3.837413440000001</v>
+      </c>
+      <c r="O92">
+        <v>-0.5756120160000001</v>
+      </c>
+      <c r="P92">
+        <v>-3.261801424000001</v>
+      </c>
+      <c r="Q92">
+        <v>-2.800801424000001</v>
+      </c>
+      <c r="R92">
+        <v>9.000000000000002</v>
+      </c>
+      <c r="S92">
+        <v>1.701619100488119</v>
+      </c>
+      <c r="T92">
+        <v>9.359060095023249</v>
+      </c>
+      <c r="U92">
+        <v>0.2388</v>
+      </c>
+      <c r="V92">
+        <v>0.06313370027210374</v>
+      </c>
+      <c r="W92">
+        <v>0.2237236723750216</v>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y92">
+        <v>0.4208913351473583</v>
+      </c>
+      <c r="Z92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <v>0.91</v>
+      </c>
+      <c r="B93">
+        <v>0.3735132151863314</v>
+      </c>
+      <c r="C93">
+        <v>-9.586577881185288</v>
+      </c>
+      <c r="D93">
+        <v>13.87054211881471</v>
+      </c>
+      <c r="E93">
+        <v>27.72512</v>
+      </c>
+      <c r="F93">
+        <v>28.05712</v>
+      </c>
+      <c r="G93">
+        <v>4.6</v>
+      </c>
+      <c r="H93">
+        <v>30.5</v>
+      </c>
+      <c r="I93">
+        <v>0</v>
+      </c>
+      <c r="J93">
+        <v>3.25</v>
+      </c>
+      <c r="K93">
+        <v>0.461</v>
+      </c>
+      <c r="L93">
+        <v>2.789</v>
+      </c>
+      <c r="M93">
+        <v>6.700040256</v>
+      </c>
+      <c r="N93">
+        <v>-3.911040256</v>
+      </c>
+      <c r="O93">
+        <v>-0.5866560384</v>
+      </c>
+      <c r="P93">
+        <v>-3.3243842176</v>
+      </c>
+      <c r="Q93">
+        <v>-2.8633842176</v>
+      </c>
+      <c r="R93">
+        <v>10.11111111111111</v>
+      </c>
+      <c r="S93">
+        <v>1.886376778320133</v>
+      </c>
+      <c r="T93">
+        <v>10.39895566113695</v>
+      </c>
+      <c r="U93">
+        <v>0.2388</v>
+      </c>
+      <c r="V93">
+        <v>0.06243992334603668</v>
+      </c>
+      <c r="W93">
+        <v>0.2238893463049665</v>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y93">
+        <v>0.4162661556402446</v>
+      </c>
+      <c r="Z93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
+        <v>0.92</v>
+      </c>
+      <c r="B94">
+        <v>0.3755132151863314</v>
+      </c>
+      <c r="C94">
+        <v>-9.97728575010893</v>
+      </c>
+      <c r="D94">
+        <v>13.78815424989107</v>
+      </c>
+      <c r="E94">
+        <v>28.03344</v>
+      </c>
+      <c r="F94">
+        <v>28.36544</v>
+      </c>
+      <c r="G94">
+        <v>4.6</v>
+      </c>
+      <c r="H94">
+        <v>30.5</v>
+      </c>
+      <c r="I94">
+        <v>0</v>
+      </c>
+      <c r="J94">
+        <v>3.25</v>
+      </c>
+      <c r="K94">
+        <v>0.461</v>
+      </c>
+      <c r="L94">
+        <v>2.789</v>
+      </c>
+      <c r="M94">
+        <v>6.773667072000001</v>
+      </c>
+      <c r="N94">
+        <v>-3.984667072000001</v>
+      </c>
+      <c r="O94">
+        <v>-0.5977000608000002</v>
+      </c>
+      <c r="P94">
+        <v>-3.386967011200001</v>
+      </c>
+      <c r="Q94">
+        <v>-2.925967011200001</v>
+      </c>
+      <c r="R94">
+        <v>11.50000000000001</v>
+      </c>
+      <c r="S94">
+        <v>2.11732387561015</v>
+      </c>
+      <c r="T94">
+        <v>11.69882511877907</v>
+      </c>
+      <c r="U94">
+        <v>0.2388</v>
+      </c>
+      <c r="V94">
+        <v>0.06176122852705802</v>
+      </c>
+      <c r="W94">
+        <v>0.2240514186277386</v>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y94">
+        <v>0.4117415235137201</v>
+      </c>
+      <c r="Z94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <v>0.93</v>
+      </c>
+      <c r="B95">
+        <v>0.3775132151863314</v>
+      </c>
+      <c r="C95">
+        <v>-10.36702066769522</v>
+      </c>
+      <c r="D95">
+        <v>13.70673933230478</v>
+      </c>
+      <c r="E95">
+        <v>28.34176</v>
+      </c>
+      <c r="F95">
+        <v>28.67376</v>
+      </c>
+      <c r="G95">
+        <v>4.6</v>
+      </c>
+      <c r="H95">
+        <v>30.5</v>
+      </c>
+      <c r="I95">
+        <v>0</v>
+      </c>
+      <c r="J95">
+        <v>3.25</v>
+      </c>
+      <c r="K95">
+        <v>0.461</v>
+      </c>
+      <c r="L95">
+        <v>2.789</v>
+      </c>
+      <c r="M95">
+        <v>6.847293888</v>
+      </c>
+      <c r="N95">
+        <v>-4.058293888</v>
+      </c>
+      <c r="O95">
+        <v>-0.6087440832</v>
+      </c>
+      <c r="P95">
+        <v>-3.4495498048</v>
+      </c>
+      <c r="Q95">
+        <v>-2.9885498048</v>
+      </c>
+      <c r="R95">
+        <v>13.2857142857143</v>
+      </c>
+      <c r="S95">
+        <v>2.414255857840172</v>
+      </c>
+      <c r="T95">
+        <v>13.37008585003322</v>
+      </c>
+      <c r="U95">
+        <v>0.2388</v>
+      </c>
+      <c r="V95">
+        <v>0.06109712929558428</v>
+      </c>
+      <c r="W95">
+        <v>0.2242100055242145</v>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y95">
+        <v>0.4073141953038952</v>
+      </c>
+      <c r="Z95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <v>0.9400000000000001</v>
+      </c>
+      <c r="B96">
+        <v>0.3795132151863314</v>
+      </c>
+      <c r="C96">
+        <v>-10.75579976773223</v>
+      </c>
+      <c r="D96">
+        <v>13.62628023226777</v>
+      </c>
+      <c r="E96">
+        <v>28.65008</v>
+      </c>
+      <c r="F96">
+        <v>28.98208</v>
+      </c>
+      <c r="G96">
+        <v>4.6</v>
+      </c>
+      <c r="H96">
+        <v>30.5</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
+      </c>
+      <c r="J96">
+        <v>3.25</v>
+      </c>
+      <c r="K96">
+        <v>0.461</v>
+      </c>
+      <c r="L96">
+        <v>2.789</v>
+      </c>
+      <c r="M96">
+        <v>6.920920704000001</v>
+      </c>
+      <c r="N96">
+        <v>-4.131920704000001</v>
+      </c>
+      <c r="O96">
+        <v>-0.6197881056000001</v>
+      </c>
+      <c r="P96">
+        <v>-3.5121325984</v>
+      </c>
+      <c r="Q96">
+        <v>-3.051132598400001</v>
+      </c>
+      <c r="R96">
+        <v>15.66666666666668</v>
+      </c>
+      <c r="S96">
+        <v>2.810165167480201</v>
+      </c>
+      <c r="T96">
+        <v>15.59843349170543</v>
+      </c>
+      <c r="U96">
+        <v>0.2388</v>
+      </c>
+      <c r="V96">
+        <v>0.06044715983499295</v>
+      </c>
+      <c r="W96">
+        <v>0.2243652182314037</v>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y96">
+        <v>0.4029810655666197</v>
+      </c>
+      <c r="Z96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97">
+        <v>0.9500000000000001</v>
+      </c>
+      <c r="B97">
+        <v>0.3815132151863315</v>
+      </c>
+      <c r="C97">
+        <v>-11.14363978405176</v>
+      </c>
+      <c r="D97">
+        <v>13.54676021594824</v>
+      </c>
+      <c r="E97">
+        <v>28.9584</v>
+      </c>
+      <c r="F97">
+        <v>29.2904</v>
+      </c>
+      <c r="G97">
+        <v>4.6</v>
+      </c>
+      <c r="H97">
+        <v>30.5</v>
+      </c>
+      <c r="I97">
+        <v>0</v>
+      </c>
+      <c r="J97">
+        <v>3.25</v>
+      </c>
+      <c r="K97">
+        <v>0.461</v>
+      </c>
+      <c r="L97">
+        <v>2.789</v>
+      </c>
+      <c r="M97">
+        <v>6.994547520000001</v>
+      </c>
+      <c r="N97">
+        <v>-4.205547520000001</v>
+      </c>
+      <c r="O97">
+        <v>-0.6308321280000002</v>
+      </c>
+      <c r="P97">
+        <v>-3.574715392000001</v>
+      </c>
+      <c r="Q97">
+        <v>-3.113715392000001</v>
+      </c>
+      <c r="R97">
+        <v>19.00000000000003</v>
+      </c>
+      <c r="S97">
+        <v>3.364438200976243</v>
+      </c>
+      <c r="T97">
+        <v>18.71812019004652</v>
+      </c>
+      <c r="U97">
+        <v>0.2388</v>
+      </c>
+      <c r="V97">
+        <v>0.05981087394199303</v>
+      </c>
+      <c r="W97">
+        <v>0.2245171633026521</v>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y97">
+        <v>0.3987391596132868</v>
+      </c>
+      <c r="Z97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <v>0.96</v>
+      </c>
+      <c r="B98">
+        <v>0.3835132151863314</v>
+      </c>
+      <c r="C98">
+        <v>-11.53055706213189</v>
+      </c>
+      <c r="D98">
+        <v>13.46816293786811</v>
+      </c>
+      <c r="E98">
+        <v>29.26672</v>
+      </c>
+      <c r="F98">
+        <v>29.59872</v>
+      </c>
+      <c r="G98">
+        <v>4.6</v>
+      </c>
+      <c r="H98">
+        <v>30.5</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="J98">
+        <v>3.25</v>
+      </c>
+      <c r="K98">
+        <v>0.461</v>
+      </c>
+      <c r="L98">
+        <v>2.789</v>
+      </c>
+      <c r="M98">
+        <v>7.068174336</v>
+      </c>
+      <c r="N98">
+        <v>-4.279174336000001</v>
+      </c>
+      <c r="O98">
+        <v>-0.6418761504</v>
+      </c>
+      <c r="P98">
+        <v>-3.637298185600001</v>
+      </c>
+      <c r="Q98">
+        <v>-3.176298185600001</v>
+      </c>
+      <c r="R98">
+        <v>23.99999999999998</v>
+      </c>
+      <c r="S98">
+        <v>4.195847751220295</v>
+      </c>
+      <c r="T98">
+        <v>23.3976502375581</v>
+      </c>
+      <c r="U98">
+        <v>0.2388</v>
+      </c>
+      <c r="V98">
+        <v>0.05918784400509727</v>
+      </c>
+      <c r="W98">
+        <v>0.2246659428515828</v>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y98">
+        <v>0.3945856267006485</v>
+      </c>
+      <c r="Z98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99">
+        <v>0.97</v>
+      </c>
+      <c r="B99">
+        <v>0.3855132151863314</v>
+      </c>
+      <c r="C99">
+        <v>-11.91656757029801</v>
+      </c>
+      <c r="D99">
+        <v>13.39047242970199</v>
+      </c>
+      <c r="E99">
+        <v>29.57504</v>
+      </c>
+      <c r="F99">
+        <v>29.90704</v>
+      </c>
+      <c r="G99">
+        <v>4.6</v>
+      </c>
+      <c r="H99">
+        <v>30.5</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+      <c r="J99">
+        <v>3.25</v>
+      </c>
+      <c r="K99">
+        <v>0.461</v>
+      </c>
+      <c r="L99">
+        <v>2.789</v>
+      </c>
+      <c r="M99">
+        <v>7.141801152</v>
+      </c>
+      <c r="N99">
+        <v>-4.352801152</v>
+      </c>
+      <c r="O99">
+        <v>-0.6529201727999999</v>
+      </c>
+      <c r="P99">
+        <v>-3.6998809792</v>
+      </c>
+      <c r="Q99">
+        <v>-3.2388809792</v>
+      </c>
+      <c r="R99">
+        <v>32.33333333333331</v>
+      </c>
+      <c r="S99">
+        <v>5.581530334960394</v>
+      </c>
+      <c r="T99">
+        <v>31.1968669834108</v>
+      </c>
+      <c r="U99">
+        <v>0.2388</v>
+      </c>
+      <c r="V99">
+        <v>0.05857766004628184</v>
+      </c>
+      <c r="W99">
+        <v>0.2248116547809479</v>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y99">
+        <v>0.390517733641879</v>
+      </c>
+      <c r="Z99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100">
+        <v>0.98</v>
+      </c>
+      <c r="B100">
+        <v>0.3875132151863314</v>
+      </c>
+      <c r="C100">
+        <v>-12.30168691053837</v>
+      </c>
+      <c r="D100">
+        <v>13.31367308946163</v>
+      </c>
+      <c r="E100">
+        <v>29.88336</v>
+      </c>
+      <c r="F100">
+        <v>30.21536</v>
+      </c>
+      <c r="G100">
+        <v>4.6</v>
+      </c>
+      <c r="H100">
+        <v>30.5</v>
+      </c>
+      <c r="I100">
+        <v>0</v>
+      </c>
+      <c r="J100">
+        <v>3.25</v>
+      </c>
+      <c r="K100">
+        <v>0.461</v>
+      </c>
+      <c r="L100">
+        <v>2.789</v>
+      </c>
+      <c r="M100">
+        <v>7.215427968</v>
+      </c>
+      <c r="N100">
+        <v>-4.426427968</v>
+      </c>
+      <c r="O100">
+        <v>-0.6639641952000001</v>
+      </c>
+      <c r="P100">
+        <v>-3.7624637728</v>
+      </c>
+      <c r="Q100">
+        <v>-3.3014637728</v>
+      </c>
+      <c r="R100">
+        <v>48.99999999999996</v>
+      </c>
+      <c r="S100">
+        <v>8.352895502440589</v>
+      </c>
+      <c r="T100">
+        <v>46.7953004751162</v>
+      </c>
+      <c r="U100">
+        <v>0.2388</v>
+      </c>
+      <c r="V100">
+        <v>0.05797992882131978</v>
+      </c>
+      <c r="W100">
+        <v>0.2249543929974689</v>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y100">
+        <v>0.3865328588087985</v>
+      </c>
+      <c r="Z100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101">
+        <v>0.99</v>
+      </c>
+      <c r="B101">
+        <v>0.3895132151863314</v>
+      </c>
+      <c r="C101">
+        <v>-12.68593032894955</v>
+      </c>
+      <c r="D101">
+        <v>13.23774967105045</v>
+      </c>
+      <c r="E101">
+        <v>30.19168</v>
+      </c>
+      <c r="F101">
+        <v>30.52368</v>
+      </c>
+      <c r="G101">
+        <v>4.6</v>
+      </c>
+      <c r="H101">
+        <v>30.5</v>
+      </c>
+      <c r="I101">
+        <v>0</v>
+      </c>
+      <c r="J101">
+        <v>3.25</v>
+      </c>
+      <c r="K101">
+        <v>0.461</v>
+      </c>
+      <c r="L101">
+        <v>2.789</v>
+      </c>
+      <c r="M101">
+        <v>7.289054784</v>
+      </c>
+      <c r="N101">
+        <v>-4.500054784</v>
+      </c>
+      <c r="O101">
+        <v>-0.6750082176</v>
+      </c>
+      <c r="P101">
+        <v>-3.8250465664</v>
+      </c>
+      <c r="Q101">
+        <v>-3.3640465664</v>
+      </c>
+      <c r="R101">
+        <v>98.99999999999991</v>
+      </c>
+      <c r="S101">
+        <v>16.66699100488118</v>
+      </c>
+      <c r="T101">
+        <v>93.5906009502324</v>
+      </c>
+      <c r="U101">
+        <v>0.2388</v>
+      </c>
+      <c r="V101">
+        <v>0.05739427297463978</v>
+      </c>
+      <c r="W101">
+        <v>0.225094247613656</v>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y101">
+        <v>0.3826284864975986</v>
+      </c>
+      <c r="Z101">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
